--- a/artfynd/A 54840-2025 artfynd.xlsx
+++ b/artfynd/A 54840-2025 artfynd.xlsx
@@ -2990,41 +2990,40 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129934450</v>
+        <v>129934386</v>
       </c>
       <c r="B25" t="n">
-        <v>5177</v>
+        <v>57733</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3034,10 +3033,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>449945</v>
+        <v>450282</v>
       </c>
       <c r="R25" t="n">
-        <v>6779066</v>
+        <v>6779221</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3078,7 +3077,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3097,45 +3095,54 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129934420</v>
+        <v>129934450</v>
       </c>
       <c r="B26" t="n">
-        <v>79081</v>
+        <v>5177</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>450467</v>
+        <v>449945</v>
       </c>
       <c r="R26" t="n">
-        <v>6779338</v>
+        <v>6779066</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3176,6 +3183,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3194,10 +3202,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129934386</v>
+        <v>129934420</v>
       </c>
       <c r="B27" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3205,42 +3213,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>450282</v>
+        <v>450467</v>
       </c>
       <c r="R27" t="n">
-        <v>6779221</v>
+        <v>6779338</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4822,10 +4822,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129934387</v>
+        <v>129934422</v>
       </c>
       <c r="B43" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4833,42 +4833,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>450145</v>
+        <v>450420</v>
       </c>
       <c r="R43" t="n">
-        <v>6779171</v>
+        <v>6779492</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4927,10 +4919,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129934385</v>
+        <v>129934424</v>
       </c>
       <c r="B44" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4938,42 +4930,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>450312</v>
+        <v>450505</v>
       </c>
       <c r="R44" t="n">
-        <v>6779288</v>
+        <v>6779559</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5032,10 +5016,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129934422</v>
+        <v>129934387</v>
       </c>
       <c r="B45" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5043,34 +5027,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>450420</v>
+        <v>450145</v>
       </c>
       <c r="R45" t="n">
-        <v>6779492</v>
+        <v>6779171</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5129,10 +5121,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129934424</v>
+        <v>129934385</v>
       </c>
       <c r="B46" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5140,34 +5132,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>450505</v>
+        <v>450312</v>
       </c>
       <c r="R46" t="n">
-        <v>6779559</v>
+        <v>6779288</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>

--- a/artfynd/A 54840-2025 artfynd.xlsx
+++ b/artfynd/A 54840-2025 artfynd.xlsx
@@ -675,53 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129934391</v>
+        <v>129934396</v>
       </c>
       <c r="B2" t="n">
-        <v>57733</v>
+        <v>97665</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>449973</v>
+        <v>450404</v>
       </c>
       <c r="R2" t="n">
-        <v>6779118</v>
+        <v>6779584</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -783,7 +775,7 @@
         <v>129934439</v>
       </c>
       <c r="B3" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129934437</v>
+        <v>129934391</v>
       </c>
       <c r="B4" t="n">
-        <v>79081</v>
+        <v>57734</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,34 +880,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>450194</v>
+        <v>449973</v>
       </c>
       <c r="R4" t="n">
-        <v>6779168</v>
+        <v>6779118</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,10 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129934433</v>
+        <v>129934437</v>
       </c>
       <c r="B5" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,10 +1009,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>450290</v>
+        <v>450194</v>
       </c>
       <c r="R5" t="n">
-        <v>6779241</v>
+        <v>6779168</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,10 +1071,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129934445</v>
+        <v>129934433</v>
       </c>
       <c r="B6" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>449962</v>
+        <v>450290</v>
       </c>
       <c r="R6" t="n">
-        <v>6779133</v>
+        <v>6779241</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,32 +1168,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129934396</v>
+        <v>129934445</v>
       </c>
       <c r="B7" t="n">
-        <v>97661</v>
+        <v>79084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1203,10 +1203,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>450404</v>
+        <v>449962</v>
       </c>
       <c r="R7" t="n">
-        <v>6779584</v>
+        <v>6779133</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1268,7 +1268,7 @@
         <v>129934384</v>
       </c>
       <c r="B8" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>129934377</v>
       </c>
       <c r="B10" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1574,10 +1574,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129934449</v>
+        <v>129934392</v>
       </c>
       <c r="B11" t="n">
-        <v>79081</v>
+        <v>57734</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1585,34 +1585,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>449874</v>
+        <v>449982</v>
       </c>
       <c r="R11" t="n">
-        <v>6779073</v>
+        <v>6779088</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1671,10 +1679,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129934392</v>
+        <v>129934449</v>
       </c>
       <c r="B12" t="n">
-        <v>57733</v>
+        <v>79084</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1682,42 +1690,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>449982</v>
+        <v>449874</v>
       </c>
       <c r="R12" t="n">
-        <v>6779088</v>
+        <v>6779073</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1779,7 +1779,7 @@
         <v>129934447</v>
       </c>
       <c r="B13" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>129934432</v>
       </c>
       <c r="B15" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2077,54 +2077,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129934406</v>
+        <v>129934440</v>
       </c>
       <c r="B16" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>450499</v>
+        <v>450114</v>
       </c>
       <c r="R16" t="n">
-        <v>6779570</v>
+        <v>6779152</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2165,7 +2156,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2184,54 +2174,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129934407</v>
+        <v>129934441</v>
       </c>
       <c r="B17" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>450494</v>
+        <v>450063</v>
       </c>
       <c r="R17" t="n">
-        <v>6779585</v>
+        <v>6779160</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2272,7 +2253,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2291,45 +2271,54 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129934440</v>
+        <v>129934406</v>
       </c>
       <c r="B18" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>450114</v>
+        <v>450499</v>
       </c>
       <c r="R18" t="n">
-        <v>6779152</v>
+        <v>6779570</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2370,6 +2359,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2388,45 +2378,54 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129934441</v>
+        <v>129934407</v>
       </c>
       <c r="B19" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>450063</v>
+        <v>450494</v>
       </c>
       <c r="R19" t="n">
-        <v>6779160</v>
+        <v>6779585</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2467,6 +2466,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2488,7 +2488,7 @@
         <v>129934442</v>
       </c>
       <c r="B20" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2582,54 +2582,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129934399</v>
+        <v>129934443</v>
       </c>
       <c r="B21" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>450362</v>
+        <v>449981</v>
       </c>
       <c r="R21" t="n">
-        <v>6779296</v>
+        <v>6779146</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2670,7 +2661,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2689,10 +2679,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129934443</v>
+        <v>129934421</v>
       </c>
       <c r="B22" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2724,10 +2714,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>449981</v>
+        <v>450436</v>
       </c>
       <c r="R22" t="n">
-        <v>6779146</v>
+        <v>6779391</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2786,7 +2776,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129934400</v>
+        <v>129934399</v>
       </c>
       <c r="B23" t="n">
         <v>8450</v>
@@ -2820,7 +2810,7 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2830,10 +2820,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>450423</v>
+        <v>450362</v>
       </c>
       <c r="R23" t="n">
-        <v>6779315</v>
+        <v>6779296</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2893,45 +2883,54 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129934421</v>
+        <v>129934400</v>
       </c>
       <c r="B24" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>450436</v>
+        <v>450423</v>
       </c>
       <c r="R24" t="n">
-        <v>6779391</v>
+        <v>6779315</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2972,6 +2971,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -2993,7 +2993,7 @@
         <v>129934386</v>
       </c>
       <c r="B25" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3095,54 +3095,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129934450</v>
+        <v>129934420</v>
       </c>
       <c r="B26" t="n">
-        <v>5177</v>
+        <v>79084</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>449945</v>
+        <v>450467</v>
       </c>
       <c r="R26" t="n">
-        <v>6779066</v>
+        <v>6779338</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3183,7 +3174,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3202,45 +3192,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129934420</v>
+        <v>129934450</v>
       </c>
       <c r="B27" t="n">
-        <v>79081</v>
+        <v>5177</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>450467</v>
+        <v>449945</v>
       </c>
       <c r="R27" t="n">
-        <v>6779338</v>
+        <v>6779066</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3281,6 +3280,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3302,7 +3302,7 @@
         <v>129934395</v>
       </c>
       <c r="B28" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3407,7 +3407,7 @@
         <v>129934427</v>
       </c>
       <c r="B29" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3504,7 +3504,7 @@
         <v>129934413</v>
       </c>
       <c r="B30" t="n">
-        <v>58106</v>
+        <v>58108</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3713,10 +3713,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129934444</v>
+        <v>129934389</v>
       </c>
       <c r="B32" t="n">
-        <v>79081</v>
+        <v>57734</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3724,34 +3724,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>449991</v>
+        <v>450060</v>
       </c>
       <c r="R32" t="n">
-        <v>6779145</v>
+        <v>6779169</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3810,10 +3818,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129934428</v>
+        <v>129934382</v>
       </c>
       <c r="B33" t="n">
-        <v>79081</v>
+        <v>57734</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3821,34 +3829,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>450417</v>
+        <v>450440</v>
       </c>
       <c r="R33" t="n">
-        <v>6779617</v>
+        <v>6779378</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3907,10 +3923,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129934389</v>
+        <v>129934393</v>
       </c>
       <c r="B34" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3950,10 +3966,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>450060</v>
+        <v>449973</v>
       </c>
       <c r="R34" t="n">
-        <v>6779169</v>
+        <v>6779075</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4012,10 +4028,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129934382</v>
+        <v>129934444</v>
       </c>
       <c r="B35" t="n">
-        <v>57733</v>
+        <v>79084</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4023,42 +4039,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>450440</v>
+        <v>449991</v>
       </c>
       <c r="R35" t="n">
-        <v>6779378</v>
+        <v>6779145</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4117,10 +4125,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129934393</v>
+        <v>129934428</v>
       </c>
       <c r="B36" t="n">
-        <v>57733</v>
+        <v>79084</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4128,42 +4136,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>449973</v>
+        <v>450417</v>
       </c>
       <c r="R36" t="n">
-        <v>6779075</v>
+        <v>6779617</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4225,7 +4225,7 @@
         <v>129934414</v>
       </c>
       <c r="B37" t="n">
-        <v>78838</v>
+        <v>78841</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4319,54 +4319,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129934405</v>
+        <v>129934431</v>
       </c>
       <c r="B38" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>450509</v>
+        <v>450414</v>
       </c>
       <c r="R38" t="n">
-        <v>6779567</v>
+        <v>6779582</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4407,7 +4398,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4426,10 +4416,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129934431</v>
+        <v>129934438</v>
       </c>
       <c r="B39" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4461,10 +4451,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>450414</v>
+        <v>450147</v>
       </c>
       <c r="R39" t="n">
-        <v>6779582</v>
+        <v>6779180</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4523,45 +4513,54 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129934438</v>
+        <v>129934405</v>
       </c>
       <c r="B40" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>450147</v>
+        <v>450509</v>
       </c>
       <c r="R40" t="n">
-        <v>6779180</v>
+        <v>6779567</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4602,6 +4601,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4623,7 +4623,7 @@
         <v>129934446</v>
       </c>
       <c r="B41" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>129934381</v>
       </c>
       <c r="B42" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4822,10 +4822,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129934422</v>
+        <v>129934387</v>
       </c>
       <c r="B43" t="n">
-        <v>79081</v>
+        <v>57734</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4833,34 +4833,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>450420</v>
+        <v>450145</v>
       </c>
       <c r="R43" t="n">
-        <v>6779492</v>
+        <v>6779171</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4919,10 +4927,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129934424</v>
+        <v>129934385</v>
       </c>
       <c r="B44" t="n">
-        <v>79081</v>
+        <v>57734</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4930,34 +4938,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>450505</v>
+        <v>450312</v>
       </c>
       <c r="R44" t="n">
-        <v>6779559</v>
+        <v>6779288</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5016,10 +5032,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129934387</v>
+        <v>129934424</v>
       </c>
       <c r="B45" t="n">
-        <v>57733</v>
+        <v>79084</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5027,42 +5043,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>450145</v>
+        <v>450505</v>
       </c>
       <c r="R45" t="n">
-        <v>6779171</v>
+        <v>6779559</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5121,10 +5129,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129934385</v>
+        <v>129934422</v>
       </c>
       <c r="B46" t="n">
-        <v>57733</v>
+        <v>79084</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5132,42 +5140,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>450312</v>
+        <v>450420</v>
       </c>
       <c r="R46" t="n">
-        <v>6779288</v>
+        <v>6779492</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5229,7 +5229,7 @@
         <v>129934390</v>
       </c>
       <c r="B47" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5331,45 +5331,54 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129934430</v>
+        <v>129934401</v>
       </c>
       <c r="B48" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>450405</v>
+        <v>450446</v>
       </c>
       <c r="R48" t="n">
-        <v>6779582</v>
+        <v>6779375</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5410,6 +5419,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5428,54 +5438,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129934401</v>
+        <v>129934430</v>
       </c>
       <c r="B49" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>450446</v>
+        <v>450405</v>
       </c>
       <c r="R49" t="n">
-        <v>6779375</v>
+        <v>6779582</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5516,7 +5517,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5535,40 +5535,41 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129934383</v>
+        <v>129934411</v>
       </c>
       <c r="B50" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
@@ -5578,10 +5579,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>450381</v>
+        <v>449925</v>
       </c>
       <c r="R50" t="n">
-        <v>6779523</v>
+        <v>6779047</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5622,6 +5623,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5640,10 +5642,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129934423</v>
+        <v>129934383</v>
       </c>
       <c r="B51" t="n">
-        <v>79081</v>
+        <v>57734</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5651,34 +5653,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>450547</v>
+        <v>450381</v>
       </c>
       <c r="R51" t="n">
-        <v>6779569</v>
+        <v>6779523</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5737,54 +5747,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129934411</v>
+        <v>129934435</v>
       </c>
       <c r="B52" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>449925</v>
+        <v>450279</v>
       </c>
       <c r="R52" t="n">
-        <v>6779047</v>
+        <v>6779222</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5825,7 +5826,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5844,10 +5844,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129934435</v>
+        <v>129934423</v>
       </c>
       <c r="B53" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5879,10 +5879,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>450279</v>
+        <v>450547</v>
       </c>
       <c r="R53" t="n">
-        <v>6779222</v>
+        <v>6779569</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5944,7 +5944,7 @@
         <v>129934429</v>
       </c>
       <c r="B54" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6038,54 +6038,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129934409</v>
+        <v>129934426</v>
       </c>
       <c r="B55" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>450379</v>
+        <v>450499</v>
       </c>
       <c r="R55" t="n">
-        <v>6779529</v>
+        <v>6779605</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6126,7 +6117,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6145,10 +6135,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129934426</v>
+        <v>129934448</v>
       </c>
       <c r="B56" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6180,10 +6170,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>450499</v>
+        <v>449939</v>
       </c>
       <c r="R56" t="n">
-        <v>6779605</v>
+        <v>6779063</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6245,7 +6235,7 @@
         <v>129934434</v>
       </c>
       <c r="B57" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6339,45 +6329,54 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129934448</v>
+        <v>129934409</v>
       </c>
       <c r="B58" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>449939</v>
+        <v>450379</v>
       </c>
       <c r="R58" t="n">
-        <v>6779063</v>
+        <v>6779529</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6418,6 +6417,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 54840-2025 artfynd.xlsx
+++ b/artfynd/A 54840-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129934396</v>
+        <v>129934439</v>
       </c>
       <c r="B2" t="n">
-        <v>97665</v>
+        <v>79084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>450404</v>
+        <v>450124</v>
       </c>
       <c r="R2" t="n">
-        <v>6779584</v>
+        <v>6779174</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129934439</v>
+        <v>129934437</v>
       </c>
       <c r="B3" t="n">
         <v>79084</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>450124</v>
+        <v>450194</v>
       </c>
       <c r="R3" t="n">
-        <v>6779174</v>
+        <v>6779168</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129934391</v>
+        <v>129934433</v>
       </c>
       <c r="B4" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,42 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>449973</v>
+        <v>450290</v>
       </c>
       <c r="R4" t="n">
-        <v>6779118</v>
+        <v>6779241</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129934437</v>
+        <v>129934445</v>
       </c>
       <c r="B5" t="n">
         <v>79084</v>
@@ -1009,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>450194</v>
+        <v>449962</v>
       </c>
       <c r="R5" t="n">
-        <v>6779168</v>
+        <v>6779133</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129934433</v>
+        <v>129934391</v>
       </c>
       <c r="B6" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1082,34 +1074,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>450290</v>
+        <v>449973</v>
       </c>
       <c r="R6" t="n">
-        <v>6779241</v>
+        <v>6779118</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,32 +1168,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129934445</v>
+        <v>129934396</v>
       </c>
       <c r="B7" t="n">
-        <v>79084</v>
+        <v>97665</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1203,10 +1203,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>449962</v>
+        <v>450404</v>
       </c>
       <c r="R7" t="n">
-        <v>6779133</v>
+        <v>6779584</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1574,40 +1574,41 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129934392</v>
+        <v>129934410</v>
       </c>
       <c r="B11" t="n">
-        <v>57734</v>
+        <v>8450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1617,10 +1618,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>449982</v>
+        <v>450367</v>
       </c>
       <c r="R11" t="n">
-        <v>6779088</v>
+        <v>6779462</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1661,6 +1662,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1679,10 +1681,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129934449</v>
+        <v>129934392</v>
       </c>
       <c r="B12" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1690,34 +1692,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>449874</v>
+        <v>449982</v>
       </c>
       <c r="R12" t="n">
-        <v>6779073</v>
+        <v>6779088</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1776,7 +1786,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129934447</v>
+        <v>129934449</v>
       </c>
       <c r="B13" t="n">
         <v>79084</v>
@@ -1811,10 +1821,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>449978</v>
+        <v>449874</v>
       </c>
       <c r="R13" t="n">
-        <v>6779085</v>
+        <v>6779073</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1873,54 +1883,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129934410</v>
+        <v>129934447</v>
       </c>
       <c r="B14" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>450367</v>
+        <v>449978</v>
       </c>
       <c r="R14" t="n">
-        <v>6779462</v>
+        <v>6779085</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1961,7 +1962,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2990,10 +2990,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129934386</v>
+        <v>129934420</v>
       </c>
       <c r="B25" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3001,42 +3001,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>450282</v>
+        <v>450467</v>
       </c>
       <c r="R25" t="n">
-        <v>6779221</v>
+        <v>6779338</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3095,10 +3087,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129934420</v>
+        <v>129934386</v>
       </c>
       <c r="B26" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3106,34 +3098,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>450467</v>
+        <v>450282</v>
       </c>
       <c r="R26" t="n">
-        <v>6779338</v>
+        <v>6779221</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3299,10 +3299,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129934395</v>
+        <v>129934427</v>
       </c>
       <c r="B28" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3310,42 +3310,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>449933</v>
+        <v>450442</v>
       </c>
       <c r="R28" t="n">
-        <v>6779073</v>
+        <v>6779630</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3404,45 +3396,53 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129934427</v>
+        <v>129934413</v>
       </c>
       <c r="B29" t="n">
-        <v>79084</v>
+        <v>58108</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>450442</v>
+        <v>449875</v>
       </c>
       <c r="R29" t="n">
-        <v>6779630</v>
+        <v>6779062</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3501,10 +3501,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129934413</v>
+        <v>129934408</v>
       </c>
       <c r="B30" t="n">
-        <v>58108</v>
+        <v>8450</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3512,29 +3512,30 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103015</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -3544,10 +3545,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>449875</v>
+        <v>450495</v>
       </c>
       <c r="R30" t="n">
-        <v>6779062</v>
+        <v>6779595</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3588,6 +3589,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3606,41 +3608,40 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129934408</v>
+        <v>129934395</v>
       </c>
       <c r="B31" t="n">
-        <v>8450</v>
+        <v>57734</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3650,10 +3651,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>450495</v>
+        <v>449933</v>
       </c>
       <c r="R31" t="n">
-        <v>6779595</v>
+        <v>6779073</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3694,7 +3695,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3713,10 +3713,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129934389</v>
+        <v>129934444</v>
       </c>
       <c r="B32" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3724,42 +3724,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>450060</v>
+        <v>449991</v>
       </c>
       <c r="R32" t="n">
-        <v>6779169</v>
+        <v>6779145</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3818,10 +3810,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129934382</v>
+        <v>129934428</v>
       </c>
       <c r="B33" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3829,42 +3821,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>450440</v>
+        <v>450417</v>
       </c>
       <c r="R33" t="n">
-        <v>6779378</v>
+        <v>6779617</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3923,7 +3907,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129934393</v>
+        <v>129934382</v>
       </c>
       <c r="B34" t="n">
         <v>57734</v>
@@ -3966,10 +3950,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>449973</v>
+        <v>450440</v>
       </c>
       <c r="R34" t="n">
-        <v>6779075</v>
+        <v>6779378</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4028,10 +4012,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129934444</v>
+        <v>129934389</v>
       </c>
       <c r="B35" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4039,34 +4023,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>449991</v>
+        <v>450060</v>
       </c>
       <c r="R35" t="n">
-        <v>6779145</v>
+        <v>6779169</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4125,10 +4117,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129934428</v>
+        <v>129934393</v>
       </c>
       <c r="B36" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4136,34 +4128,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>450417</v>
+        <v>449973</v>
       </c>
       <c r="R36" t="n">
-        <v>6779617</v>
+        <v>6779075</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4822,10 +4822,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129934387</v>
+        <v>129934422</v>
       </c>
       <c r="B43" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4833,42 +4833,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>450145</v>
+        <v>450420</v>
       </c>
       <c r="R43" t="n">
-        <v>6779171</v>
+        <v>6779492</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4927,10 +4919,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129934385</v>
+        <v>129934424</v>
       </c>
       <c r="B44" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4938,42 +4930,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>450312</v>
+        <v>450505</v>
       </c>
       <c r="R44" t="n">
-        <v>6779288</v>
+        <v>6779559</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5032,10 +5016,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129934424</v>
+        <v>129934385</v>
       </c>
       <c r="B45" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5043,34 +5027,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>450505</v>
+        <v>450312</v>
       </c>
       <c r="R45" t="n">
-        <v>6779559</v>
+        <v>6779288</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5129,10 +5121,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129934422</v>
+        <v>129934387</v>
       </c>
       <c r="B46" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5140,34 +5132,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>450420</v>
+        <v>450145</v>
       </c>
       <c r="R46" t="n">
-        <v>6779492</v>
+        <v>6779171</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5331,54 +5331,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129934401</v>
+        <v>129934430</v>
       </c>
       <c r="B48" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>450446</v>
+        <v>450405</v>
       </c>
       <c r="R48" t="n">
-        <v>6779375</v>
+        <v>6779582</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5419,7 +5410,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5438,45 +5428,54 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129934430</v>
+        <v>129934401</v>
       </c>
       <c r="B49" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>450405</v>
+        <v>450446</v>
       </c>
       <c r="R49" t="n">
-        <v>6779582</v>
+        <v>6779375</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5517,6 +5516,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5535,54 +5535,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129934411</v>
+        <v>129934423</v>
       </c>
       <c r="B50" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>449925</v>
+        <v>450547</v>
       </c>
       <c r="R50" t="n">
-        <v>6779047</v>
+        <v>6779569</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5623,7 +5614,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5642,10 +5632,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129934383</v>
+        <v>129934435</v>
       </c>
       <c r="B51" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5653,42 +5643,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>450381</v>
+        <v>450279</v>
       </c>
       <c r="R51" t="n">
-        <v>6779523</v>
+        <v>6779222</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5747,10 +5729,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129934435</v>
+        <v>129934383</v>
       </c>
       <c r="B52" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5758,34 +5740,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>450279</v>
+        <v>450381</v>
       </c>
       <c r="R52" t="n">
-        <v>6779222</v>
+        <v>6779523</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5844,45 +5834,54 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129934423</v>
+        <v>129934411</v>
       </c>
       <c r="B53" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>450547</v>
+        <v>449925</v>
       </c>
       <c r="R53" t="n">
-        <v>6779569</v>
+        <v>6779047</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5923,6 +5922,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6135,7 +6135,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129934448</v>
+        <v>129934434</v>
       </c>
       <c r="B56" t="n">
         <v>79084</v>
@@ -6170,10 +6170,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>449939</v>
+        <v>450296</v>
       </c>
       <c r="R56" t="n">
-        <v>6779063</v>
+        <v>6779230</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6232,7 +6232,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129934434</v>
+        <v>129934448</v>
       </c>
       <c r="B57" t="n">
         <v>79084</v>
@@ -6267,10 +6267,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>450296</v>
+        <v>449939</v>
       </c>
       <c r="R57" t="n">
-        <v>6779230</v>
+        <v>6779063</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>

--- a/artfynd/A 54840-2025 artfynd.xlsx
+++ b/artfynd/A 54840-2025 artfynd.xlsx
@@ -1063,53 +1063,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129934391</v>
+        <v>129934396</v>
       </c>
       <c r="B6" t="n">
-        <v>57734</v>
+        <v>97665</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>449973</v>
+        <v>450404</v>
       </c>
       <c r="R6" t="n">
-        <v>6779118</v>
+        <v>6779584</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,45 +1160,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129934396</v>
+        <v>129934391</v>
       </c>
       <c r="B7" t="n">
-        <v>97665</v>
+        <v>57734</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>450404</v>
+        <v>449973</v>
       </c>
       <c r="R7" t="n">
-        <v>6779584</v>
+        <v>6779118</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1681,10 +1681,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129934392</v>
+        <v>129934449</v>
       </c>
       <c r="B12" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1692,42 +1692,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>449982</v>
+        <v>449874</v>
       </c>
       <c r="R12" t="n">
-        <v>6779088</v>
+        <v>6779073</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1786,7 +1778,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129934449</v>
+        <v>129934447</v>
       </c>
       <c r="B13" t="n">
         <v>79084</v>
@@ -1821,10 +1813,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>449874</v>
+        <v>449978</v>
       </c>
       <c r="R13" t="n">
-        <v>6779073</v>
+        <v>6779085</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1883,10 +1875,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129934447</v>
+        <v>129934392</v>
       </c>
       <c r="B14" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1894,34 +1886,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>449978</v>
+        <v>449982</v>
       </c>
       <c r="R14" t="n">
-        <v>6779085</v>
+        <v>6779088</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2271,7 +2271,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129934406</v>
+        <v>129934407</v>
       </c>
       <c r="B18" t="n">
         <v>8450</v>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>450499</v>
+        <v>450494</v>
       </c>
       <c r="R18" t="n">
-        <v>6779570</v>
+        <v>6779585</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2378,7 +2378,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129934407</v>
+        <v>129934406</v>
       </c>
       <c r="B19" t="n">
         <v>8450</v>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>450494</v>
+        <v>450499</v>
       </c>
       <c r="R19" t="n">
-        <v>6779585</v>
+        <v>6779570</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3299,45 +3299,53 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129934427</v>
+        <v>129934413</v>
       </c>
       <c r="B28" t="n">
-        <v>79084</v>
+        <v>58108</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>450442</v>
+        <v>449875</v>
       </c>
       <c r="R28" t="n">
-        <v>6779630</v>
+        <v>6779062</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3396,53 +3404,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129934413</v>
+        <v>129934427</v>
       </c>
       <c r="B29" t="n">
-        <v>58108</v>
+        <v>79084</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>449875</v>
+        <v>450442</v>
       </c>
       <c r="R29" t="n">
-        <v>6779062</v>
+        <v>6779630</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3501,41 +3501,40 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129934408</v>
+        <v>129934395</v>
       </c>
       <c r="B30" t="n">
-        <v>8450</v>
+        <v>57734</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -3545,10 +3544,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>450495</v>
+        <v>449933</v>
       </c>
       <c r="R30" t="n">
-        <v>6779595</v>
+        <v>6779073</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3589,7 +3588,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3608,40 +3606,41 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129934395</v>
+        <v>129934408</v>
       </c>
       <c r="B31" t="n">
-        <v>57734</v>
+        <v>8450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3651,10 +3650,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>449933</v>
+        <v>450495</v>
       </c>
       <c r="R31" t="n">
-        <v>6779073</v>
+        <v>6779595</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3695,6 +3694,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3713,10 +3713,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129934444</v>
+        <v>129934382</v>
       </c>
       <c r="B32" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3724,34 +3724,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>449991</v>
+        <v>450440</v>
       </c>
       <c r="R32" t="n">
-        <v>6779145</v>
+        <v>6779378</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3810,10 +3818,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129934428</v>
+        <v>129934389</v>
       </c>
       <c r="B33" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3821,34 +3829,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>450417</v>
+        <v>450060</v>
       </c>
       <c r="R33" t="n">
-        <v>6779617</v>
+        <v>6779169</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3907,7 +3923,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129934382</v>
+        <v>129934393</v>
       </c>
       <c r="B34" t="n">
         <v>57734</v>
@@ -3950,10 +3966,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>450440</v>
+        <v>449973</v>
       </c>
       <c r="R34" t="n">
-        <v>6779378</v>
+        <v>6779075</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4012,10 +4028,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129934389</v>
+        <v>129934444</v>
       </c>
       <c r="B35" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4023,42 +4039,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>450060</v>
+        <v>449991</v>
       </c>
       <c r="R35" t="n">
-        <v>6779169</v>
+        <v>6779145</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4117,10 +4125,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129934393</v>
+        <v>129934428</v>
       </c>
       <c r="B36" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4128,42 +4136,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>449973</v>
+        <v>450417</v>
       </c>
       <c r="R36" t="n">
-        <v>6779075</v>
+        <v>6779617</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5226,10 +5226,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129934390</v>
+        <v>129934430</v>
       </c>
       <c r="B47" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5237,42 +5237,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>450070</v>
+        <v>450405</v>
       </c>
       <c r="R47" t="n">
-        <v>6779152</v>
+        <v>6779582</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5331,10 +5323,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129934430</v>
+        <v>129934390</v>
       </c>
       <c r="B48" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5342,34 +5334,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>450405</v>
+        <v>450070</v>
       </c>
       <c r="R48" t="n">
-        <v>6779582</v>
+        <v>6779152</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>

--- a/artfynd/A 54840-2025 artfynd.xlsx
+++ b/artfynd/A 54840-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129934439</v>
       </c>
       <c r="B2" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129934437</v>
       </c>
       <c r="B3" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129934433</v>
       </c>
       <c r="B4" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129934445</v>
       </c>
       <c r="B5" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,45 +1063,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129934396</v>
+        <v>129934391</v>
       </c>
       <c r="B6" t="n">
-        <v>97665</v>
+        <v>57737</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>450404</v>
+        <v>449973</v>
       </c>
       <c r="R6" t="n">
-        <v>6779584</v>
+        <v>6779118</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,53 +1168,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129934391</v>
+        <v>129934396</v>
       </c>
       <c r="B7" t="n">
-        <v>57734</v>
+        <v>97668</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>449973</v>
+        <v>450404</v>
       </c>
       <c r="R7" t="n">
-        <v>6779118</v>
+        <v>6779584</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1268,7 +1268,7 @@
         <v>129934384</v>
       </c>
       <c r="B8" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>129934402</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>129934377</v>
       </c>
       <c r="B10" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>129934410</v>
       </c>
       <c r="B11" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>129934449</v>
       </c>
       <c r="B12" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>129934447</v>
       </c>
       <c r="B13" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>129934392</v>
       </c>
       <c r="B14" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1980,10 +1980,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129934432</v>
+        <v>129934440</v>
       </c>
       <c r="B15" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2015,10 +2015,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>450400</v>
+        <v>450114</v>
       </c>
       <c r="R15" t="n">
-        <v>6779534</v>
+        <v>6779152</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2077,10 +2077,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129934440</v>
+        <v>129934441</v>
       </c>
       <c r="B16" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2112,10 +2112,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>450114</v>
+        <v>450063</v>
       </c>
       <c r="R16" t="n">
-        <v>6779152</v>
+        <v>6779160</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2174,10 +2174,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129934441</v>
+        <v>129934432</v>
       </c>
       <c r="B17" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2209,10 +2209,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>450063</v>
+        <v>450400</v>
       </c>
       <c r="R17" t="n">
-        <v>6779160</v>
+        <v>6779534</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2271,10 +2271,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129934407</v>
+        <v>129934406</v>
       </c>
       <c r="B18" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>450494</v>
+        <v>450499</v>
       </c>
       <c r="R18" t="n">
-        <v>6779585</v>
+        <v>6779570</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2378,10 +2378,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129934406</v>
+        <v>129934407</v>
       </c>
       <c r="B19" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>450499</v>
+        <v>450494</v>
       </c>
       <c r="R19" t="n">
-        <v>6779570</v>
+        <v>6779585</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2488,7 +2488,7 @@
         <v>129934442</v>
       </c>
       <c r="B20" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>129934443</v>
       </c>
       <c r="B21" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>129934421</v>
       </c>
       <c r="B22" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>129934399</v>
       </c>
       <c r="B23" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>129934400</v>
       </c>
       <c r="B24" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2990,45 +2990,54 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129934420</v>
+        <v>129934450</v>
       </c>
       <c r="B25" t="n">
-        <v>79084</v>
+        <v>5177</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>450467</v>
+        <v>449945</v>
       </c>
       <c r="R25" t="n">
-        <v>6779338</v>
+        <v>6779066</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3069,6 +3078,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3087,10 +3097,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129934386</v>
+        <v>129934420</v>
       </c>
       <c r="B26" t="n">
-        <v>57734</v>
+        <v>79087</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3098,42 +3108,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>450282</v>
+        <v>450467</v>
       </c>
       <c r="R26" t="n">
-        <v>6779221</v>
+        <v>6779338</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3192,41 +3194,40 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129934450</v>
+        <v>129934386</v>
       </c>
       <c r="B27" t="n">
-        <v>5177</v>
+        <v>57737</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3236,10 +3237,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>449945</v>
+        <v>450282</v>
       </c>
       <c r="R27" t="n">
-        <v>6779066</v>
+        <v>6779221</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3280,7 +3281,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3299,10 +3299,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129934413</v>
+        <v>129934408</v>
       </c>
       <c r="B28" t="n">
-        <v>58108</v>
+        <v>8451</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3310,29 +3310,30 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103015</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3342,10 +3343,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>449875</v>
+        <v>450495</v>
       </c>
       <c r="R28" t="n">
-        <v>6779062</v>
+        <v>6779595</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3386,6 +3387,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3407,7 +3409,7 @@
         <v>129934427</v>
       </c>
       <c r="B29" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3504,7 +3506,7 @@
         <v>129934395</v>
       </c>
       <c r="B30" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3606,10 +3608,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129934408</v>
+        <v>129934413</v>
       </c>
       <c r="B31" t="n">
-        <v>8450</v>
+        <v>58111</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3617,30 +3619,29 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>103015</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3650,10 +3651,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>450495</v>
+        <v>449875</v>
       </c>
       <c r="R31" t="n">
-        <v>6779595</v>
+        <v>6779062</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3694,7 +3695,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3713,10 +3713,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129934382</v>
+        <v>129934444</v>
       </c>
       <c r="B32" t="n">
-        <v>57734</v>
+        <v>79087</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3724,42 +3724,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>450440</v>
+        <v>449991</v>
       </c>
       <c r="R32" t="n">
-        <v>6779378</v>
+        <v>6779145</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3818,10 +3810,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129934389</v>
+        <v>129934428</v>
       </c>
       <c r="B33" t="n">
-        <v>57734</v>
+        <v>79087</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3829,42 +3821,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>450060</v>
+        <v>450417</v>
       </c>
       <c r="R33" t="n">
-        <v>6779169</v>
+        <v>6779617</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3923,10 +3907,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129934393</v>
+        <v>129934382</v>
       </c>
       <c r="B34" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3966,10 +3950,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>449973</v>
+        <v>450440</v>
       </c>
       <c r="R34" t="n">
-        <v>6779075</v>
+        <v>6779378</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4028,10 +4012,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129934444</v>
+        <v>129934389</v>
       </c>
       <c r="B35" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4039,34 +4023,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>449991</v>
+        <v>450060</v>
       </c>
       <c r="R35" t="n">
-        <v>6779145</v>
+        <v>6779169</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4125,10 +4117,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129934428</v>
+        <v>129934393</v>
       </c>
       <c r="B36" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4136,34 +4128,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>450417</v>
+        <v>449973</v>
       </c>
       <c r="R36" t="n">
-        <v>6779617</v>
+        <v>6779075</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4222,45 +4222,54 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129934414</v>
+        <v>129934405</v>
       </c>
       <c r="B37" t="n">
-        <v>78841</v>
+        <v>8451</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>450423</v>
+        <v>450509</v>
       </c>
       <c r="R37" t="n">
-        <v>6779566</v>
+        <v>6779567</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4301,6 +4310,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4319,10 +4329,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129934431</v>
+        <v>129934414</v>
       </c>
       <c r="B38" t="n">
-        <v>79084</v>
+        <v>78844</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4330,21 +4340,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4354,10 +4364,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>450414</v>
+        <v>450423</v>
       </c>
       <c r="R38" t="n">
-        <v>6779582</v>
+        <v>6779566</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4416,10 +4426,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129934438</v>
+        <v>129934431</v>
       </c>
       <c r="B39" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4451,10 +4461,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>450147</v>
+        <v>450414</v>
       </c>
       <c r="R39" t="n">
-        <v>6779180</v>
+        <v>6779582</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4513,54 +4523,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129934405</v>
+        <v>129934438</v>
       </c>
       <c r="B40" t="n">
-        <v>8450</v>
+        <v>79087</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>450509</v>
+        <v>450147</v>
       </c>
       <c r="R40" t="n">
-        <v>6779567</v>
+        <v>6779180</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4601,7 +4602,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4623,7 +4623,7 @@
         <v>129934446</v>
       </c>
       <c r="B41" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>129934381</v>
       </c>
       <c r="B42" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>129934422</v>
       </c>
       <c r="B43" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4922,7 +4922,7 @@
         <v>129934424</v>
       </c>
       <c r="B44" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
         <v>129934385</v>
       </c>
       <c r="B45" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5124,7 +5124,7 @@
         <v>129934387</v>
       </c>
       <c r="B46" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5226,10 +5226,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129934430</v>
+        <v>129934390</v>
       </c>
       <c r="B47" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5237,34 +5237,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>450405</v>
+        <v>450070</v>
       </c>
       <c r="R47" t="n">
-        <v>6779582</v>
+        <v>6779152</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5323,10 +5331,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129934390</v>
+        <v>129934430</v>
       </c>
       <c r="B48" t="n">
-        <v>57734</v>
+        <v>79087</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5334,42 +5342,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>450070</v>
+        <v>450405</v>
       </c>
       <c r="R48" t="n">
-        <v>6779152</v>
+        <v>6779582</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5431,7 +5431,7 @@
         <v>129934401</v>
       </c>
       <c r="B49" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5535,10 +5535,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129934423</v>
+        <v>129934383</v>
       </c>
       <c r="B50" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5546,34 +5546,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>450547</v>
+        <v>450381</v>
       </c>
       <c r="R50" t="n">
-        <v>6779569</v>
+        <v>6779523</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5632,10 +5640,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129934435</v>
+        <v>129934423</v>
       </c>
       <c r="B51" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5667,10 +5675,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>450279</v>
+        <v>450547</v>
       </c>
       <c r="R51" t="n">
-        <v>6779222</v>
+        <v>6779569</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5729,10 +5737,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129934383</v>
+        <v>129934435</v>
       </c>
       <c r="B52" t="n">
-        <v>57734</v>
+        <v>79087</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5740,42 +5748,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>450381</v>
+        <v>450279</v>
       </c>
       <c r="R52" t="n">
-        <v>6779523</v>
+        <v>6779222</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5837,7 +5837,7 @@
         <v>129934411</v>
       </c>
       <c r="B53" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5944,7 +5944,7 @@
         <v>129934429</v>
       </c>
       <c r="B54" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6038,10 +6038,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129934426</v>
+        <v>129934448</v>
       </c>
       <c r="B55" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6073,10 +6073,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>450499</v>
+        <v>449939</v>
       </c>
       <c r="R55" t="n">
-        <v>6779605</v>
+        <v>6779063</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6135,10 +6135,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129934434</v>
+        <v>129934426</v>
       </c>
       <c r="B56" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6170,10 +6170,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>450296</v>
+        <v>450499</v>
       </c>
       <c r="R56" t="n">
-        <v>6779230</v>
+        <v>6779605</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6232,10 +6232,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129934448</v>
+        <v>129934434</v>
       </c>
       <c r="B57" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6267,10 +6267,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>449939</v>
+        <v>450296</v>
       </c>
       <c r="R57" t="n">
-        <v>6779063</v>
+        <v>6779230</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6332,7 +6332,7 @@
         <v>129934409</v>
       </c>
       <c r="B58" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 54840-2025 artfynd.xlsx
+++ b/artfynd/A 54840-2025 artfynd.xlsx
@@ -4222,54 +4222,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129934405</v>
+        <v>129934431</v>
       </c>
       <c r="B37" t="n">
-        <v>8451</v>
+        <v>79087</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>450509</v>
+        <v>450414</v>
       </c>
       <c r="R37" t="n">
-        <v>6779567</v>
+        <v>6779582</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4310,7 +4301,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4329,10 +4319,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129934414</v>
+        <v>129934438</v>
       </c>
       <c r="B38" t="n">
-        <v>78844</v>
+        <v>79087</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4340,21 +4330,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4364,10 +4354,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>450423</v>
+        <v>450147</v>
       </c>
       <c r="R38" t="n">
-        <v>6779566</v>
+        <v>6779180</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4426,45 +4416,54 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129934431</v>
+        <v>129934405</v>
       </c>
       <c r="B39" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>450414</v>
+        <v>450509</v>
       </c>
       <c r="R39" t="n">
-        <v>6779582</v>
+        <v>6779567</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4505,6 +4504,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4523,10 +4523,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129934438</v>
+        <v>129934414</v>
       </c>
       <c r="B40" t="n">
-        <v>79087</v>
+        <v>78844</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4534,21 +4534,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4558,10 +4558,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>450147</v>
+        <v>450423</v>
       </c>
       <c r="R40" t="n">
-        <v>6779180</v>
+        <v>6779566</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5226,10 +5226,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129934390</v>
+        <v>129934430</v>
       </c>
       <c r="B47" t="n">
-        <v>57737</v>
+        <v>79087</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5237,42 +5237,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>450070</v>
+        <v>450405</v>
       </c>
       <c r="R47" t="n">
-        <v>6779152</v>
+        <v>6779582</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5331,45 +5323,54 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129934430</v>
+        <v>129934401</v>
       </c>
       <c r="B48" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>450405</v>
+        <v>450446</v>
       </c>
       <c r="R48" t="n">
-        <v>6779582</v>
+        <v>6779375</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5410,6 +5411,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5428,41 +5430,40 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129934401</v>
+        <v>129934390</v>
       </c>
       <c r="B49" t="n">
-        <v>8451</v>
+        <v>57737</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -5472,10 +5473,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>450446</v>
+        <v>450070</v>
       </c>
       <c r="R49" t="n">
-        <v>6779375</v>
+        <v>6779152</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5516,7 +5517,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6038,7 +6038,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129934448</v>
+        <v>129934426</v>
       </c>
       <c r="B55" t="n">
         <v>79087</v>
@@ -6073,10 +6073,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>449939</v>
+        <v>450499</v>
       </c>
       <c r="R55" t="n">
-        <v>6779063</v>
+        <v>6779605</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6135,7 +6135,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129934426</v>
+        <v>129934434</v>
       </c>
       <c r="B56" t="n">
         <v>79087</v>
@@ -6170,10 +6170,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>450499</v>
+        <v>450296</v>
       </c>
       <c r="R56" t="n">
-        <v>6779605</v>
+        <v>6779230</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6232,7 +6232,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129934434</v>
+        <v>129934448</v>
       </c>
       <c r="B57" t="n">
         <v>79087</v>
@@ -6267,10 +6267,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>450296</v>
+        <v>449939</v>
       </c>
       <c r="R57" t="n">
-        <v>6779230</v>
+        <v>6779063</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>

--- a/artfynd/A 54840-2025 artfynd.xlsx
+++ b/artfynd/A 54840-2025 artfynd.xlsx
@@ -3713,7 +3713,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129934444</v>
+        <v>129934428</v>
       </c>
       <c r="B32" t="n">
         <v>79087</v>
@@ -3748,10 +3748,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>449991</v>
+        <v>450417</v>
       </c>
       <c r="R32" t="n">
-        <v>6779145</v>
+        <v>6779617</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3810,10 +3810,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129934428</v>
+        <v>129934382</v>
       </c>
       <c r="B33" t="n">
-        <v>79087</v>
+        <v>57737</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3821,34 +3821,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>450417</v>
+        <v>450440</v>
       </c>
       <c r="R33" t="n">
-        <v>6779617</v>
+        <v>6779378</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3907,7 +3915,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129934382</v>
+        <v>129934389</v>
       </c>
       <c r="B34" t="n">
         <v>57737</v>
@@ -3950,10 +3958,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>450440</v>
+        <v>450060</v>
       </c>
       <c r="R34" t="n">
-        <v>6779378</v>
+        <v>6779169</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4012,7 +4020,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129934389</v>
+        <v>129934393</v>
       </c>
       <c r="B35" t="n">
         <v>57737</v>
@@ -4055,10 +4063,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>450060</v>
+        <v>449973</v>
       </c>
       <c r="R35" t="n">
-        <v>6779169</v>
+        <v>6779075</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4117,10 +4125,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129934393</v>
+        <v>129934444</v>
       </c>
       <c r="B36" t="n">
-        <v>57737</v>
+        <v>79087</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4128,42 +4136,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>449973</v>
+        <v>449991</v>
       </c>
       <c r="R36" t="n">
-        <v>6779075</v>
+        <v>6779145</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4222,10 +4222,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129934431</v>
+        <v>129934414</v>
       </c>
       <c r="B37" t="n">
-        <v>79087</v>
+        <v>78844</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4233,21 +4233,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4257,10 +4257,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>450414</v>
+        <v>450423</v>
       </c>
       <c r="R37" t="n">
-        <v>6779582</v>
+        <v>6779566</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4319,7 +4319,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129934438</v>
+        <v>129934431</v>
       </c>
       <c r="B38" t="n">
         <v>79087</v>
@@ -4354,10 +4354,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>450147</v>
+        <v>450414</v>
       </c>
       <c r="R38" t="n">
-        <v>6779180</v>
+        <v>6779582</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4416,54 +4416,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129934405</v>
+        <v>129934438</v>
       </c>
       <c r="B39" t="n">
-        <v>8451</v>
+        <v>79087</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>450509</v>
+        <v>450147</v>
       </c>
       <c r="R39" t="n">
-        <v>6779567</v>
+        <v>6779180</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4504,7 +4495,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4523,45 +4513,54 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129934414</v>
+        <v>129934405</v>
       </c>
       <c r="B40" t="n">
-        <v>78844</v>
+        <v>8451</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>450423</v>
+        <v>450509</v>
       </c>
       <c r="R40" t="n">
-        <v>6779566</v>
+        <v>6779567</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4602,6 +4601,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5323,41 +5323,40 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129934401</v>
+        <v>129934390</v>
       </c>
       <c r="B48" t="n">
-        <v>8451</v>
+        <v>57737</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -5367,10 +5366,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>450446</v>
+        <v>450070</v>
       </c>
       <c r="R48" t="n">
-        <v>6779375</v>
+        <v>6779152</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5411,7 +5410,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5430,40 +5428,41 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129934390</v>
+        <v>129934401</v>
       </c>
       <c r="B49" t="n">
-        <v>57737</v>
+        <v>8451</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -5473,10 +5472,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>450070</v>
+        <v>450446</v>
       </c>
       <c r="R49" t="n">
-        <v>6779152</v>
+        <v>6779375</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5517,6 +5516,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 54840-2025 artfynd.xlsx
+++ b/artfynd/A 54840-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129934439</v>
+        <v>129934391</v>
       </c>
       <c r="B2" t="n">
-        <v>79087</v>
+        <v>57737</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>450124</v>
+        <v>449973</v>
       </c>
       <c r="R2" t="n">
-        <v>6779174</v>
+        <v>6779118</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +780,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129934437</v>
+        <v>129934396</v>
       </c>
       <c r="B3" t="n">
-        <v>79087</v>
+        <v>97669</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>450194</v>
+        <v>450404</v>
       </c>
       <c r="R3" t="n">
-        <v>6779168</v>
+        <v>6779584</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129934433</v>
+        <v>129934439</v>
       </c>
       <c r="B4" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>450290</v>
+        <v>450124</v>
       </c>
       <c r="R4" t="n">
-        <v>6779241</v>
+        <v>6779174</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129934445</v>
+        <v>129934437</v>
       </c>
       <c r="B5" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,10 +1009,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>449962</v>
+        <v>450194</v>
       </c>
       <c r="R5" t="n">
-        <v>6779133</v>
+        <v>6779168</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1071,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129934391</v>
+        <v>129934433</v>
       </c>
       <c r="B6" t="n">
-        <v>57737</v>
+        <v>79088</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,42 +1082,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>449973</v>
+        <v>450290</v>
       </c>
       <c r="R6" t="n">
-        <v>6779118</v>
+        <v>6779241</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,32 +1168,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129934396</v>
+        <v>129934445</v>
       </c>
       <c r="B7" t="n">
-        <v>97668</v>
+        <v>79088</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1203,10 +1203,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>450404</v>
+        <v>449962</v>
       </c>
       <c r="R7" t="n">
-        <v>6779584</v>
+        <v>6779133</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1480,7 +1480,7 @@
         <v>129934377</v>
       </c>
       <c r="B10" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1574,54 +1574,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129934410</v>
+        <v>129934449</v>
       </c>
       <c r="B11" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>450367</v>
+        <v>449874</v>
       </c>
       <c r="R11" t="n">
-        <v>6779462</v>
+        <v>6779073</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1662,7 +1653,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1681,10 +1671,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129934449</v>
+        <v>129934447</v>
       </c>
       <c r="B12" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1716,10 +1706,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>449874</v>
+        <v>449978</v>
       </c>
       <c r="R12" t="n">
-        <v>6779073</v>
+        <v>6779085</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1778,10 +1768,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129934447</v>
+        <v>129934392</v>
       </c>
       <c r="B13" t="n">
-        <v>79087</v>
+        <v>57737</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1789,34 +1779,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>449978</v>
+        <v>449982</v>
       </c>
       <c r="R13" t="n">
-        <v>6779085</v>
+        <v>6779088</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1875,40 +1873,41 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129934392</v>
+        <v>129934410</v>
       </c>
       <c r="B14" t="n">
-        <v>57737</v>
+        <v>8451</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1918,10 +1917,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>449982</v>
+        <v>450367</v>
       </c>
       <c r="R14" t="n">
-        <v>6779088</v>
+        <v>6779462</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1962,6 +1961,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1980,10 +1980,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129934440</v>
+        <v>129934432</v>
       </c>
       <c r="B15" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2015,10 +2015,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>450114</v>
+        <v>450400</v>
       </c>
       <c r="R15" t="n">
-        <v>6779152</v>
+        <v>6779534</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2077,10 +2077,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129934441</v>
+        <v>129934440</v>
       </c>
       <c r="B16" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2112,10 +2112,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>450063</v>
+        <v>450114</v>
       </c>
       <c r="R16" t="n">
-        <v>6779160</v>
+        <v>6779152</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2174,10 +2174,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129934432</v>
+        <v>129934441</v>
       </c>
       <c r="B17" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2209,10 +2209,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>450400</v>
+        <v>450063</v>
       </c>
       <c r="R17" t="n">
-        <v>6779534</v>
+        <v>6779160</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2271,7 +2271,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129934406</v>
+        <v>129934407</v>
       </c>
       <c r="B18" t="n">
         <v>8451</v>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>450499</v>
+        <v>450494</v>
       </c>
       <c r="R18" t="n">
-        <v>6779570</v>
+        <v>6779585</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2378,7 +2378,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129934407</v>
+        <v>129934406</v>
       </c>
       <c r="B19" t="n">
         <v>8451</v>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>450494</v>
+        <v>450499</v>
       </c>
       <c r="R19" t="n">
-        <v>6779585</v>
+        <v>6779570</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2488,7 +2488,7 @@
         <v>129934442</v>
       </c>
       <c r="B20" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>129934443</v>
       </c>
       <c r="B21" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>129934421</v>
       </c>
       <c r="B22" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2990,54 +2990,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129934450</v>
+        <v>129934420</v>
       </c>
       <c r="B25" t="n">
-        <v>5177</v>
+        <v>79088</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>449945</v>
+        <v>450467</v>
       </c>
       <c r="R25" t="n">
-        <v>6779066</v>
+        <v>6779338</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3078,7 +3069,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3097,10 +3087,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129934420</v>
+        <v>129934386</v>
       </c>
       <c r="B26" t="n">
-        <v>79087</v>
+        <v>57737</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3108,34 +3098,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>450467</v>
+        <v>450282</v>
       </c>
       <c r="R26" t="n">
-        <v>6779338</v>
+        <v>6779221</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3194,40 +3192,41 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129934386</v>
+        <v>129934450</v>
       </c>
       <c r="B27" t="n">
-        <v>57737</v>
+        <v>5177</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3237,10 +3236,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>450282</v>
+        <v>449945</v>
       </c>
       <c r="R27" t="n">
-        <v>6779221</v>
+        <v>6779066</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3281,6 +3280,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3299,41 +3299,40 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129934408</v>
+        <v>129934395</v>
       </c>
       <c r="B28" t="n">
-        <v>8451</v>
+        <v>57737</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3343,10 +3342,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>450495</v>
+        <v>449933</v>
       </c>
       <c r="R28" t="n">
-        <v>6779595</v>
+        <v>6779073</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3387,7 +3386,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3409,7 +3407,7 @@
         <v>129934427</v>
       </c>
       <c r="B29" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3503,40 +3501,41 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129934395</v>
+        <v>129934408</v>
       </c>
       <c r="B30" t="n">
-        <v>57737</v>
+        <v>8451</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -3546,10 +3545,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>449933</v>
+        <v>450495</v>
       </c>
       <c r="R30" t="n">
-        <v>6779073</v>
+        <v>6779595</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3590,6 +3589,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3713,10 +3713,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129934428</v>
+        <v>129934444</v>
       </c>
       <c r="B32" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3748,10 +3748,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>450417</v>
+        <v>449991</v>
       </c>
       <c r="R32" t="n">
-        <v>6779617</v>
+        <v>6779145</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3810,10 +3810,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129934382</v>
+        <v>129934428</v>
       </c>
       <c r="B33" t="n">
-        <v>57737</v>
+        <v>79088</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3821,42 +3821,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>450440</v>
+        <v>450417</v>
       </c>
       <c r="R33" t="n">
-        <v>6779378</v>
+        <v>6779617</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3915,7 +3907,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129934389</v>
+        <v>129934382</v>
       </c>
       <c r="B34" t="n">
         <v>57737</v>
@@ -3958,10 +3950,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>450060</v>
+        <v>450440</v>
       </c>
       <c r="R34" t="n">
-        <v>6779169</v>
+        <v>6779378</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4020,7 +4012,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129934393</v>
+        <v>129934389</v>
       </c>
       <c r="B35" t="n">
         <v>57737</v>
@@ -4063,10 +4055,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>449973</v>
+        <v>450060</v>
       </c>
       <c r="R35" t="n">
-        <v>6779075</v>
+        <v>6779169</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4125,10 +4117,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129934444</v>
+        <v>129934393</v>
       </c>
       <c r="B36" t="n">
-        <v>79087</v>
+        <v>57737</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4136,34 +4128,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>449991</v>
+        <v>449973</v>
       </c>
       <c r="R36" t="n">
-        <v>6779145</v>
+        <v>6779075</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4222,10 +4222,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129934414</v>
+        <v>129934431</v>
       </c>
       <c r="B37" t="n">
-        <v>78844</v>
+        <v>79088</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4233,21 +4233,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4257,10 +4257,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>450423</v>
+        <v>450414</v>
       </c>
       <c r="R37" t="n">
-        <v>6779566</v>
+        <v>6779582</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4319,10 +4319,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129934431</v>
+        <v>129934438</v>
       </c>
       <c r="B38" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4354,10 +4354,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>450414</v>
+        <v>450147</v>
       </c>
       <c r="R38" t="n">
-        <v>6779582</v>
+        <v>6779180</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4416,10 +4416,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129934438</v>
+        <v>129934414</v>
       </c>
       <c r="B39" t="n">
-        <v>79087</v>
+        <v>78845</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4427,21 +4427,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4451,10 +4451,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>450147</v>
+        <v>450423</v>
       </c>
       <c r="R39" t="n">
-        <v>6779180</v>
+        <v>6779566</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4623,7 +4623,7 @@
         <v>129934446</v>
       </c>
       <c r="B41" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>129934422</v>
       </c>
       <c r="B43" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4922,7 +4922,7 @@
         <v>129934424</v>
       </c>
       <c r="B44" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5226,10 +5226,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129934430</v>
+        <v>129934390</v>
       </c>
       <c r="B47" t="n">
-        <v>79087</v>
+        <v>57737</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5237,34 +5237,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>450405</v>
+        <v>450070</v>
       </c>
       <c r="R47" t="n">
-        <v>6779582</v>
+        <v>6779152</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5323,10 +5331,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129934390</v>
+        <v>129934430</v>
       </c>
       <c r="B48" t="n">
-        <v>57737</v>
+        <v>79088</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5334,42 +5342,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>450070</v>
+        <v>450405</v>
       </c>
       <c r="R48" t="n">
-        <v>6779152</v>
+        <v>6779582</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5643,7 +5643,7 @@
         <v>129934423</v>
       </c>
       <c r="B51" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
         <v>129934435</v>
       </c>
       <c r="B52" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5944,7 +5944,7 @@
         <v>129934429</v>
       </c>
       <c r="B54" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6041,7 +6041,7 @@
         <v>129934426</v>
       </c>
       <c r="B55" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6138,7 +6138,7 @@
         <v>129934434</v>
       </c>
       <c r="B56" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         <v>129934448</v>
       </c>
       <c r="B57" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 54840-2025 artfynd.xlsx
+++ b/artfynd/A 54840-2025 artfynd.xlsx
@@ -1574,10 +1574,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129934449</v>
+        <v>129934392</v>
       </c>
       <c r="B11" t="n">
-        <v>79088</v>
+        <v>57737</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1585,34 +1585,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>449874</v>
+        <v>449982</v>
       </c>
       <c r="R11" t="n">
-        <v>6779073</v>
+        <v>6779088</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1671,7 +1679,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129934447</v>
+        <v>129934449</v>
       </c>
       <c r="B12" t="n">
         <v>79088</v>
@@ -1706,10 +1714,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>449978</v>
+        <v>449874</v>
       </c>
       <c r="R12" t="n">
-        <v>6779085</v>
+        <v>6779073</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1768,10 +1776,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129934392</v>
+        <v>129934447</v>
       </c>
       <c r="B13" t="n">
-        <v>57737</v>
+        <v>79088</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1779,42 +1787,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>449982</v>
+        <v>449978</v>
       </c>
       <c r="R13" t="n">
-        <v>6779088</v>
+        <v>6779085</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2485,45 +2485,54 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129934442</v>
+        <v>129934399</v>
       </c>
       <c r="B20" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>449998</v>
+        <v>450362</v>
       </c>
       <c r="R20" t="n">
-        <v>6779110</v>
+        <v>6779296</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2564,6 +2573,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2582,45 +2592,54 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129934443</v>
+        <v>129934400</v>
       </c>
       <c r="B21" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>449981</v>
+        <v>450423</v>
       </c>
       <c r="R21" t="n">
-        <v>6779146</v>
+        <v>6779315</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2661,6 +2680,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2679,7 +2699,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129934421</v>
+        <v>129934442</v>
       </c>
       <c r="B22" t="n">
         <v>79088</v>
@@ -2714,10 +2734,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>450436</v>
+        <v>449998</v>
       </c>
       <c r="R22" t="n">
-        <v>6779391</v>
+        <v>6779110</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2776,54 +2796,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129934399</v>
+        <v>129934443</v>
       </c>
       <c r="B23" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>450362</v>
+        <v>449981</v>
       </c>
       <c r="R23" t="n">
-        <v>6779296</v>
+        <v>6779146</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2864,7 +2875,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2883,54 +2893,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129934400</v>
+        <v>129934421</v>
       </c>
       <c r="B24" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>450423</v>
+        <v>450436</v>
       </c>
       <c r="R24" t="n">
-        <v>6779315</v>
+        <v>6779391</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2971,7 +2972,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -2990,10 +2990,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129934420</v>
+        <v>129934386</v>
       </c>
       <c r="B25" t="n">
-        <v>79088</v>
+        <v>57737</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3001,34 +3001,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>450467</v>
+        <v>450282</v>
       </c>
       <c r="R25" t="n">
-        <v>6779338</v>
+        <v>6779221</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3087,10 +3095,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129934386</v>
+        <v>129934420</v>
       </c>
       <c r="B26" t="n">
-        <v>57737</v>
+        <v>79088</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3098,42 +3106,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>450282</v>
+        <v>450467</v>
       </c>
       <c r="R26" t="n">
-        <v>6779221</v>
+        <v>6779338</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -4222,45 +4222,54 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129934431</v>
+        <v>129934405</v>
       </c>
       <c r="B37" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>450414</v>
+        <v>450509</v>
       </c>
       <c r="R37" t="n">
-        <v>6779582</v>
+        <v>6779567</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4301,6 +4310,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4319,7 +4329,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129934438</v>
+        <v>129934431</v>
       </c>
       <c r="B38" t="n">
         <v>79088</v>
@@ -4354,10 +4364,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>450147</v>
+        <v>450414</v>
       </c>
       <c r="R38" t="n">
-        <v>6779180</v>
+        <v>6779582</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4416,10 +4426,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129934414</v>
+        <v>129934438</v>
       </c>
       <c r="B39" t="n">
-        <v>78845</v>
+        <v>79088</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4427,21 +4437,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4451,10 +4461,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>450423</v>
+        <v>450147</v>
       </c>
       <c r="R39" t="n">
-        <v>6779566</v>
+        <v>6779180</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4513,54 +4523,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129934405</v>
+        <v>129934414</v>
       </c>
       <c r="B40" t="n">
-        <v>8451</v>
+        <v>78845</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>450509</v>
+        <v>450423</v>
       </c>
       <c r="R40" t="n">
-        <v>6779567</v>
+        <v>6779566</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4601,7 +4602,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 54840-2025 artfynd.xlsx
+++ b/artfynd/A 54840-2025 artfynd.xlsx
@@ -1574,10 +1574,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129934392</v>
+        <v>129934449</v>
       </c>
       <c r="B11" t="n">
-        <v>57737</v>
+        <v>79088</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1585,42 +1585,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>449982</v>
+        <v>449874</v>
       </c>
       <c r="R11" t="n">
-        <v>6779088</v>
+        <v>6779073</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1679,7 +1671,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129934449</v>
+        <v>129934447</v>
       </c>
       <c r="B12" t="n">
         <v>79088</v>
@@ -1714,10 +1706,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>449874</v>
+        <v>449978</v>
       </c>
       <c r="R12" t="n">
-        <v>6779073</v>
+        <v>6779085</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1776,10 +1768,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129934447</v>
+        <v>129934392</v>
       </c>
       <c r="B13" t="n">
-        <v>79088</v>
+        <v>57737</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1787,34 +1779,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>449978</v>
+        <v>449982</v>
       </c>
       <c r="R13" t="n">
-        <v>6779085</v>
+        <v>6779088</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2990,10 +2990,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129934386</v>
+        <v>129934420</v>
       </c>
       <c r="B25" t="n">
-        <v>57737</v>
+        <v>79088</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3001,42 +3001,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>450282</v>
+        <v>450467</v>
       </c>
       <c r="R25" t="n">
-        <v>6779221</v>
+        <v>6779338</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3095,10 +3087,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129934420</v>
+        <v>129934386</v>
       </c>
       <c r="B26" t="n">
-        <v>79088</v>
+        <v>57737</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3106,34 +3098,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>450467</v>
+        <v>450282</v>
       </c>
       <c r="R26" t="n">
-        <v>6779338</v>
+        <v>6779221</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -4222,54 +4222,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129934405</v>
+        <v>129934431</v>
       </c>
       <c r="B37" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>450509</v>
+        <v>450414</v>
       </c>
       <c r="R37" t="n">
-        <v>6779567</v>
+        <v>6779582</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4310,7 +4301,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4329,7 +4319,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129934431</v>
+        <v>129934438</v>
       </c>
       <c r="B38" t="n">
         <v>79088</v>
@@ -4364,10 +4354,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>450414</v>
+        <v>450147</v>
       </c>
       <c r="R38" t="n">
-        <v>6779582</v>
+        <v>6779180</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4426,10 +4416,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129934438</v>
+        <v>129934414</v>
       </c>
       <c r="B39" t="n">
-        <v>79088</v>
+        <v>78845</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4437,21 +4427,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4461,10 +4451,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>450147</v>
+        <v>450423</v>
       </c>
       <c r="R39" t="n">
-        <v>6779180</v>
+        <v>6779566</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4523,45 +4513,54 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129934414</v>
+        <v>129934405</v>
       </c>
       <c r="B40" t="n">
-        <v>78845</v>
+        <v>8451</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>450423</v>
+        <v>450509</v>
       </c>
       <c r="R40" t="n">
-        <v>6779566</v>
+        <v>6779567</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4602,6 +4601,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5535,10 +5535,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129934383</v>
+        <v>129934423</v>
       </c>
       <c r="B50" t="n">
-        <v>57737</v>
+        <v>79088</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5546,42 +5546,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>450381</v>
+        <v>450547</v>
       </c>
       <c r="R50" t="n">
-        <v>6779523</v>
+        <v>6779569</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5640,7 +5632,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129934423</v>
+        <v>129934435</v>
       </c>
       <c r="B51" t="n">
         <v>79088</v>
@@ -5675,10 +5667,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>450547</v>
+        <v>450279</v>
       </c>
       <c r="R51" t="n">
-        <v>6779569</v>
+        <v>6779222</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5737,10 +5729,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129934435</v>
+        <v>129934383</v>
       </c>
       <c r="B52" t="n">
-        <v>79088</v>
+        <v>57737</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5748,34 +5740,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>450279</v>
+        <v>450381</v>
       </c>
       <c r="R52" t="n">
-        <v>6779222</v>
+        <v>6779523</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>

--- a/artfynd/A 54840-2025 artfynd.xlsx
+++ b/artfynd/A 54840-2025 artfynd.xlsx
@@ -780,32 +780,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129934396</v>
+        <v>129934439</v>
       </c>
       <c r="B3" t="n">
-        <v>97669</v>
+        <v>79089</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -815,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>450404</v>
+        <v>450124</v>
       </c>
       <c r="R3" t="n">
-        <v>6779584</v>
+        <v>6779174</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129934439</v>
+        <v>129934437</v>
       </c>
       <c r="B4" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>450124</v>
+        <v>450194</v>
       </c>
       <c r="R4" t="n">
-        <v>6779174</v>
+        <v>6779168</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,10 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129934437</v>
+        <v>129934433</v>
       </c>
       <c r="B5" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,10 +1009,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>450194</v>
+        <v>450290</v>
       </c>
       <c r="R5" t="n">
-        <v>6779168</v>
+        <v>6779241</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,10 +1071,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129934433</v>
+        <v>129934445</v>
       </c>
       <c r="B6" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>450290</v>
+        <v>449962</v>
       </c>
       <c r="R6" t="n">
-        <v>6779241</v>
+        <v>6779133</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,32 +1168,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129934445</v>
+        <v>129934396</v>
       </c>
       <c r="B7" t="n">
-        <v>79088</v>
+        <v>97686</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1203,10 +1203,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>449962</v>
+        <v>450404</v>
       </c>
       <c r="R7" t="n">
-        <v>6779133</v>
+        <v>6779584</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1480,7 +1480,7 @@
         <v>129934377</v>
       </c>
       <c r="B10" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1574,10 +1574,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129934449</v>
+        <v>129934392</v>
       </c>
       <c r="B11" t="n">
-        <v>79088</v>
+        <v>57737</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1585,34 +1585,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>449874</v>
+        <v>449982</v>
       </c>
       <c r="R11" t="n">
-        <v>6779073</v>
+        <v>6779088</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1671,10 +1679,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129934447</v>
+        <v>129934449</v>
       </c>
       <c r="B12" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1706,10 +1714,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>449978</v>
+        <v>449874</v>
       </c>
       <c r="R12" t="n">
-        <v>6779085</v>
+        <v>6779073</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1768,10 +1776,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129934392</v>
+        <v>129934447</v>
       </c>
       <c r="B13" t="n">
-        <v>57737</v>
+        <v>79089</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1779,42 +1787,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>449982</v>
+        <v>449978</v>
       </c>
       <c r="R13" t="n">
-        <v>6779088</v>
+        <v>6779085</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1983,7 +1983,7 @@
         <v>129934432</v>
       </c>
       <c r="B15" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>129934440</v>
       </c>
       <c r="B16" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>129934441</v>
       </c>
       <c r="B17" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2485,54 +2485,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129934399</v>
+        <v>129934442</v>
       </c>
       <c r="B20" t="n">
-        <v>8451</v>
+        <v>79089</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>450362</v>
+        <v>449998</v>
       </c>
       <c r="R20" t="n">
-        <v>6779296</v>
+        <v>6779110</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2573,7 +2564,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2592,54 +2582,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129934400</v>
+        <v>129934443</v>
       </c>
       <c r="B21" t="n">
-        <v>8451</v>
+        <v>79089</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>450423</v>
+        <v>449981</v>
       </c>
       <c r="R21" t="n">
-        <v>6779315</v>
+        <v>6779146</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2680,7 +2661,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2699,10 +2679,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129934442</v>
+        <v>129934421</v>
       </c>
       <c r="B22" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2734,10 +2714,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>449998</v>
+        <v>450436</v>
       </c>
       <c r="R22" t="n">
-        <v>6779110</v>
+        <v>6779391</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2796,45 +2776,54 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129934443</v>
+        <v>129934399</v>
       </c>
       <c r="B23" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>449981</v>
+        <v>450362</v>
       </c>
       <c r="R23" t="n">
-        <v>6779146</v>
+        <v>6779296</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2875,6 +2864,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2893,45 +2883,54 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129934421</v>
+        <v>129934400</v>
       </c>
       <c r="B24" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>450436</v>
+        <v>450423</v>
       </c>
       <c r="R24" t="n">
-        <v>6779391</v>
+        <v>6779315</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2972,6 +2971,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -2990,10 +2990,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129934420</v>
+        <v>129934386</v>
       </c>
       <c r="B25" t="n">
-        <v>79088</v>
+        <v>57737</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3001,34 +3001,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>450467</v>
+        <v>450282</v>
       </c>
       <c r="R25" t="n">
-        <v>6779338</v>
+        <v>6779221</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3087,40 +3095,41 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129934386</v>
+        <v>129934450</v>
       </c>
       <c r="B26" t="n">
-        <v>57737</v>
+        <v>5177</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3130,10 +3139,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>450282</v>
+        <v>449945</v>
       </c>
       <c r="R26" t="n">
-        <v>6779221</v>
+        <v>6779066</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3174,6 +3183,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3192,54 +3202,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129934450</v>
+        <v>129934420</v>
       </c>
       <c r="B27" t="n">
-        <v>5177</v>
+        <v>79089</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>449945</v>
+        <v>450467</v>
       </c>
       <c r="R27" t="n">
-        <v>6779066</v>
+        <v>6779338</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3280,7 +3281,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3407,7 +3407,7 @@
         <v>129934427</v>
       </c>
       <c r="B29" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3501,10 +3501,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129934408</v>
+        <v>129934413</v>
       </c>
       <c r="B30" t="n">
-        <v>8451</v>
+        <v>58112</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3512,30 +3512,29 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>103015</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -3545,10 +3544,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>450495</v>
+        <v>449875</v>
       </c>
       <c r="R30" t="n">
-        <v>6779595</v>
+        <v>6779062</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3589,7 +3588,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3608,10 +3606,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129934413</v>
+        <v>129934408</v>
       </c>
       <c r="B31" t="n">
-        <v>58111</v>
+        <v>8451</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3619,29 +3617,30 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103015</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3651,10 +3650,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>449875</v>
+        <v>450495</v>
       </c>
       <c r="R31" t="n">
-        <v>6779062</v>
+        <v>6779595</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3695,6 +3694,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3713,10 +3713,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129934444</v>
+        <v>129934389</v>
       </c>
       <c r="B32" t="n">
-        <v>79088</v>
+        <v>57737</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3724,34 +3724,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>449991</v>
+        <v>450060</v>
       </c>
       <c r="R32" t="n">
-        <v>6779145</v>
+        <v>6779169</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3810,10 +3818,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129934428</v>
+        <v>129934444</v>
       </c>
       <c r="B33" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3845,10 +3853,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>450417</v>
+        <v>449991</v>
       </c>
       <c r="R33" t="n">
-        <v>6779617</v>
+        <v>6779145</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3907,10 +3915,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129934382</v>
+        <v>129934428</v>
       </c>
       <c r="B34" t="n">
-        <v>57737</v>
+        <v>79089</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3918,42 +3926,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>450440</v>
+        <v>450417</v>
       </c>
       <c r="R34" t="n">
-        <v>6779378</v>
+        <v>6779617</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4012,7 +4012,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129934389</v>
+        <v>129934382</v>
       </c>
       <c r="B35" t="n">
         <v>57737</v>
@@ -4055,10 +4055,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>450060</v>
+        <v>450440</v>
       </c>
       <c r="R35" t="n">
-        <v>6779169</v>
+        <v>6779378</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4222,45 +4222,54 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129934431</v>
+        <v>129934405</v>
       </c>
       <c r="B37" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>450414</v>
+        <v>450509</v>
       </c>
       <c r="R37" t="n">
-        <v>6779582</v>
+        <v>6779567</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4301,6 +4310,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4319,10 +4329,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129934438</v>
+        <v>129934414</v>
       </c>
       <c r="B38" t="n">
-        <v>79088</v>
+        <v>78846</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4330,21 +4340,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4354,10 +4364,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>450147</v>
+        <v>450423</v>
       </c>
       <c r="R38" t="n">
-        <v>6779180</v>
+        <v>6779566</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4416,10 +4426,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129934414</v>
+        <v>129934431</v>
       </c>
       <c r="B39" t="n">
-        <v>78845</v>
+        <v>79089</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4427,21 +4437,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4451,10 +4461,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>450423</v>
+        <v>450414</v>
       </c>
       <c r="R39" t="n">
-        <v>6779566</v>
+        <v>6779582</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4513,54 +4523,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129934405</v>
+        <v>129934438</v>
       </c>
       <c r="B40" t="n">
-        <v>8451</v>
+        <v>79089</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>450509</v>
+        <v>450147</v>
       </c>
       <c r="R40" t="n">
-        <v>6779567</v>
+        <v>6779180</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4601,7 +4602,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4623,7 +4623,7 @@
         <v>129934446</v>
       </c>
       <c r="B41" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4822,10 +4822,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129934422</v>
+        <v>129934385</v>
       </c>
       <c r="B43" t="n">
-        <v>79088</v>
+        <v>57737</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4833,34 +4833,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>450420</v>
+        <v>450312</v>
       </c>
       <c r="R43" t="n">
-        <v>6779492</v>
+        <v>6779288</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4919,10 +4927,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129934424</v>
+        <v>129934387</v>
       </c>
       <c r="B44" t="n">
-        <v>79088</v>
+        <v>57737</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4930,34 +4938,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>450505</v>
+        <v>450145</v>
       </c>
       <c r="R44" t="n">
-        <v>6779559</v>
+        <v>6779171</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5016,10 +5032,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129934385</v>
+        <v>129934422</v>
       </c>
       <c r="B45" t="n">
-        <v>57737</v>
+        <v>79089</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5027,42 +5043,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>450312</v>
+        <v>450420</v>
       </c>
       <c r="R45" t="n">
-        <v>6779288</v>
+        <v>6779492</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5121,10 +5129,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129934387</v>
+        <v>129934424</v>
       </c>
       <c r="B46" t="n">
-        <v>57737</v>
+        <v>79089</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5132,42 +5140,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>450145</v>
+        <v>450505</v>
       </c>
       <c r="R46" t="n">
-        <v>6779171</v>
+        <v>6779559</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5334,7 +5334,7 @@
         <v>129934430</v>
       </c>
       <c r="B48" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5535,10 +5535,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129934423</v>
+        <v>129934383</v>
       </c>
       <c r="B50" t="n">
-        <v>79088</v>
+        <v>57737</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5546,34 +5546,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>450547</v>
+        <v>450381</v>
       </c>
       <c r="R50" t="n">
-        <v>6779569</v>
+        <v>6779523</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5632,10 +5640,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129934435</v>
+        <v>129934423</v>
       </c>
       <c r="B51" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5667,10 +5675,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>450279</v>
+        <v>450547</v>
       </c>
       <c r="R51" t="n">
-        <v>6779222</v>
+        <v>6779569</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5729,10 +5737,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129934383</v>
+        <v>129934435</v>
       </c>
       <c r="B52" t="n">
-        <v>57737</v>
+        <v>79089</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5740,42 +5748,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>450381</v>
+        <v>450279</v>
       </c>
       <c r="R52" t="n">
-        <v>6779523</v>
+        <v>6779222</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5944,7 +5944,7 @@
         <v>129934429</v>
       </c>
       <c r="B54" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6038,45 +6038,54 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129934426</v>
+        <v>129934409</v>
       </c>
       <c r="B55" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>450499</v>
+        <v>450379</v>
       </c>
       <c r="R55" t="n">
-        <v>6779605</v>
+        <v>6779529</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6117,6 +6126,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6135,10 +6145,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129934434</v>
+        <v>129934426</v>
       </c>
       <c r="B56" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6170,10 +6180,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>450296</v>
+        <v>450499</v>
       </c>
       <c r="R56" t="n">
-        <v>6779230</v>
+        <v>6779605</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6232,10 +6242,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129934448</v>
+        <v>129934434</v>
       </c>
       <c r="B57" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6267,10 +6277,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>449939</v>
+        <v>450296</v>
       </c>
       <c r="R57" t="n">
-        <v>6779063</v>
+        <v>6779230</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6329,54 +6339,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129934409</v>
+        <v>129934448</v>
       </c>
       <c r="B58" t="n">
-        <v>8451</v>
+        <v>79089</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>450379</v>
+        <v>449939</v>
       </c>
       <c r="R58" t="n">
-        <v>6779529</v>
+        <v>6779063</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6417,7 +6418,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 54840-2025 artfynd.xlsx
+++ b/artfynd/A 54840-2025 artfynd.xlsx
@@ -1265,41 +1265,40 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129934402</v>
+        <v>129934384</v>
       </c>
       <c r="B8" t="n">
-        <v>8451</v>
+        <v>57738</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1309,10 +1308,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>450440</v>
+        <v>450390</v>
       </c>
       <c r="R8" t="n">
-        <v>6779378</v>
+        <v>6779506</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1353,7 +1352,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1372,40 +1370,41 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129934384</v>
+        <v>129934402</v>
       </c>
       <c r="B9" t="n">
-        <v>57738</v>
+        <v>8451</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1415,10 +1414,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>450390</v>
+        <v>450440</v>
       </c>
       <c r="R9" t="n">
-        <v>6779506</v>
+        <v>6779378</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1459,6 +1458,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1980,45 +1980,54 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129934432</v>
+        <v>129934406</v>
       </c>
       <c r="B15" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>450400</v>
+        <v>450499</v>
       </c>
       <c r="R15" t="n">
-        <v>6779534</v>
+        <v>6779570</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2059,6 +2068,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2077,45 +2087,54 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129934440</v>
+        <v>129934407</v>
       </c>
       <c r="B16" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>450114</v>
+        <v>450494</v>
       </c>
       <c r="R16" t="n">
-        <v>6779152</v>
+        <v>6779585</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2156,6 +2175,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2174,7 +2194,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129934441</v>
+        <v>129934432</v>
       </c>
       <c r="B17" t="n">
         <v>79095</v>
@@ -2209,10 +2229,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>450063</v>
+        <v>450400</v>
       </c>
       <c r="R17" t="n">
-        <v>6779160</v>
+        <v>6779534</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2271,54 +2291,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129934406</v>
+        <v>129934440</v>
       </c>
       <c r="B18" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>450499</v>
+        <v>450114</v>
       </c>
       <c r="R18" t="n">
-        <v>6779570</v>
+        <v>6779152</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2359,7 +2370,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2378,54 +2388,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129934407</v>
+        <v>129934441</v>
       </c>
       <c r="B19" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>450494</v>
+        <v>450063</v>
       </c>
       <c r="R19" t="n">
-        <v>6779585</v>
+        <v>6779160</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2466,7 +2467,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 54840-2025 artfynd.xlsx
+++ b/artfynd/A 54840-2025 artfynd.xlsx
@@ -2485,54 +2485,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129934399</v>
+        <v>129934442</v>
       </c>
       <c r="B20" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>450362</v>
+        <v>449998</v>
       </c>
       <c r="R20" t="n">
-        <v>6779296</v>
+        <v>6779110</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2573,7 +2564,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2592,54 +2582,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129934400</v>
+        <v>129934443</v>
       </c>
       <c r="B21" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>450423</v>
+        <v>449981</v>
       </c>
       <c r="R21" t="n">
-        <v>6779315</v>
+        <v>6779146</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2680,7 +2661,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2699,7 +2679,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129934442</v>
+        <v>129934421</v>
       </c>
       <c r="B22" t="n">
         <v>79095</v>
@@ -2734,10 +2714,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>449998</v>
+        <v>450436</v>
       </c>
       <c r="R22" t="n">
-        <v>6779110</v>
+        <v>6779391</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2796,45 +2776,54 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129934443</v>
+        <v>129934399</v>
       </c>
       <c r="B23" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>449981</v>
+        <v>450362</v>
       </c>
       <c r="R23" t="n">
-        <v>6779146</v>
+        <v>6779296</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2875,6 +2864,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2893,45 +2883,54 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129934421</v>
+        <v>129934400</v>
       </c>
       <c r="B24" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>450436</v>
+        <v>450423</v>
       </c>
       <c r="R24" t="n">
-        <v>6779391</v>
+        <v>6779315</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2972,6 +2971,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 54840-2025 artfynd.xlsx
+++ b/artfynd/A 54840-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129934439</v>
+        <v>129934396</v>
       </c>
       <c r="B2" t="n">
-        <v>79095</v>
+        <v>97704</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>450124</v>
+        <v>450404</v>
       </c>
       <c r="R2" t="n">
-        <v>6779174</v>
+        <v>6779584</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129934437</v>
+        <v>129934391</v>
       </c>
       <c r="B3" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>450194</v>
+        <v>449973</v>
       </c>
       <c r="R3" t="n">
-        <v>6779168</v>
+        <v>6779118</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,7 +877,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129934433</v>
+        <v>129934439</v>
       </c>
       <c r="B4" t="n">
         <v>79095</v>
@@ -904,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>450290</v>
+        <v>450124</v>
       </c>
       <c r="R4" t="n">
-        <v>6779241</v>
+        <v>6779174</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,7 +974,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129934445</v>
+        <v>129934437</v>
       </c>
       <c r="B5" t="n">
         <v>79095</v>
@@ -1001,10 +1009,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>449962</v>
+        <v>450194</v>
       </c>
       <c r="R5" t="n">
-        <v>6779133</v>
+        <v>6779168</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1071,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129934396</v>
+        <v>129934433</v>
       </c>
       <c r="B6" t="n">
-        <v>97702</v>
+        <v>79095</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1106,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>450404</v>
+        <v>450290</v>
       </c>
       <c r="R6" t="n">
-        <v>6779584</v>
+        <v>6779241</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1168,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129934391</v>
+        <v>129934445</v>
       </c>
       <c r="B7" t="n">
-        <v>57738</v>
+        <v>79095</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,42 +1179,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>449973</v>
+        <v>449962</v>
       </c>
       <c r="R7" t="n">
-        <v>6779118</v>
+        <v>6779133</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1574,10 +1574,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129934449</v>
+        <v>129934392</v>
       </c>
       <c r="B11" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1585,34 +1585,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>449874</v>
+        <v>449982</v>
       </c>
       <c r="R11" t="n">
-        <v>6779073</v>
+        <v>6779088</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1671,7 +1679,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129934447</v>
+        <v>129934449</v>
       </c>
       <c r="B12" t="n">
         <v>79095</v>
@@ -1706,10 +1714,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>449978</v>
+        <v>449874</v>
       </c>
       <c r="R12" t="n">
-        <v>6779085</v>
+        <v>6779073</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1768,10 +1776,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129934392</v>
+        <v>129934447</v>
       </c>
       <c r="B13" t="n">
-        <v>57738</v>
+        <v>79095</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1779,42 +1787,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>449982</v>
+        <v>449978</v>
       </c>
       <c r="R13" t="n">
-        <v>6779088</v>
+        <v>6779085</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1980,54 +1980,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129934406</v>
+        <v>129934440</v>
       </c>
       <c r="B15" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>450499</v>
+        <v>450114</v>
       </c>
       <c r="R15" t="n">
-        <v>6779570</v>
+        <v>6779152</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2068,7 +2059,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2087,7 +2077,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129934407</v>
+        <v>129934406</v>
       </c>
       <c r="B16" t="n">
         <v>8451</v>
@@ -2131,10 +2121,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>450494</v>
+        <v>450499</v>
       </c>
       <c r="R16" t="n">
-        <v>6779585</v>
+        <v>6779570</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2194,45 +2184,54 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129934432</v>
+        <v>129934407</v>
       </c>
       <c r="B17" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>450400</v>
+        <v>450494</v>
       </c>
       <c r="R17" t="n">
-        <v>6779534</v>
+        <v>6779585</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2273,6 +2272,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2291,7 +2291,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129934440</v>
+        <v>129934432</v>
       </c>
       <c r="B18" t="n">
         <v>79095</v>
@@ -2326,10 +2326,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>450114</v>
+        <v>450400</v>
       </c>
       <c r="R18" t="n">
-        <v>6779152</v>
+        <v>6779534</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2990,40 +2990,41 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129934386</v>
+        <v>129934450</v>
       </c>
       <c r="B25" t="n">
-        <v>57738</v>
+        <v>5177</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3033,10 +3034,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>450282</v>
+        <v>449945</v>
       </c>
       <c r="R25" t="n">
-        <v>6779221</v>
+        <v>6779066</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3077,6 +3078,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3095,10 +3097,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129934420</v>
+        <v>129934386</v>
       </c>
       <c r="B26" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3106,34 +3108,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>450467</v>
+        <v>450282</v>
       </c>
       <c r="R26" t="n">
-        <v>6779338</v>
+        <v>6779221</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3192,54 +3202,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129934450</v>
+        <v>129934420</v>
       </c>
       <c r="B27" t="n">
-        <v>5177</v>
+        <v>79095</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>449945</v>
+        <v>450467</v>
       </c>
       <c r="R27" t="n">
-        <v>6779066</v>
+        <v>6779338</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3280,7 +3281,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3299,53 +3299,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129934413</v>
+        <v>129934427</v>
       </c>
       <c r="B28" t="n">
-        <v>58113</v>
+        <v>79095</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>449875</v>
+        <v>450442</v>
       </c>
       <c r="R28" t="n">
-        <v>6779062</v>
+        <v>6779630</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3404,45 +3396,53 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129934427</v>
+        <v>129934413</v>
       </c>
       <c r="B29" t="n">
-        <v>79095</v>
+        <v>58113</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>450442</v>
+        <v>449875</v>
       </c>
       <c r="R29" t="n">
-        <v>6779630</v>
+        <v>6779062</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3713,10 +3713,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129934444</v>
+        <v>129934382</v>
       </c>
       <c r="B32" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3724,34 +3724,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>449991</v>
+        <v>450440</v>
       </c>
       <c r="R32" t="n">
-        <v>6779145</v>
+        <v>6779378</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3810,10 +3818,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129934428</v>
+        <v>129934389</v>
       </c>
       <c r="B33" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3821,34 +3829,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>450417</v>
+        <v>450060</v>
       </c>
       <c r="R33" t="n">
-        <v>6779617</v>
+        <v>6779169</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3907,7 +3923,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129934382</v>
+        <v>129934393</v>
       </c>
       <c r="B34" t="n">
         <v>57738</v>
@@ -3950,10 +3966,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>450440</v>
+        <v>449973</v>
       </c>
       <c r="R34" t="n">
-        <v>6779378</v>
+        <v>6779075</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4012,10 +4028,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129934389</v>
+        <v>129934444</v>
       </c>
       <c r="B35" t="n">
-        <v>57738</v>
+        <v>79095</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4023,42 +4039,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>450060</v>
+        <v>449991</v>
       </c>
       <c r="R35" t="n">
-        <v>6779169</v>
+        <v>6779145</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4117,10 +4125,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129934393</v>
+        <v>129934428</v>
       </c>
       <c r="B36" t="n">
-        <v>57738</v>
+        <v>79095</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4128,42 +4136,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>449973</v>
+        <v>450417</v>
       </c>
       <c r="R36" t="n">
-        <v>6779075</v>
+        <v>6779617</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4222,45 +4222,54 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129934431</v>
+        <v>129934405</v>
       </c>
       <c r="B37" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>450414</v>
+        <v>450509</v>
       </c>
       <c r="R37" t="n">
-        <v>6779582</v>
+        <v>6779567</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4301,6 +4310,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4319,10 +4329,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129934438</v>
+        <v>129934414</v>
       </c>
       <c r="B38" t="n">
-        <v>79095</v>
+        <v>78852</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4330,21 +4340,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4354,10 +4364,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>450147</v>
+        <v>450423</v>
       </c>
       <c r="R38" t="n">
-        <v>6779180</v>
+        <v>6779566</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4416,10 +4426,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129934414</v>
+        <v>129934431</v>
       </c>
       <c r="B39" t="n">
-        <v>78852</v>
+        <v>79095</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4427,21 +4437,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4451,10 +4461,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>450423</v>
+        <v>450414</v>
       </c>
       <c r="R39" t="n">
-        <v>6779566</v>
+        <v>6779582</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4513,54 +4523,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129934405</v>
+        <v>129934438</v>
       </c>
       <c r="B40" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>450509</v>
+        <v>450147</v>
       </c>
       <c r="R40" t="n">
-        <v>6779567</v>
+        <v>6779180</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4601,7 +4602,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4822,10 +4822,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129934422</v>
+        <v>129934385</v>
       </c>
       <c r="B43" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4833,34 +4833,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>450420</v>
+        <v>450312</v>
       </c>
       <c r="R43" t="n">
-        <v>6779492</v>
+        <v>6779288</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4919,10 +4927,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129934424</v>
+        <v>129934387</v>
       </c>
       <c r="B44" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4930,34 +4938,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>450505</v>
+        <v>450145</v>
       </c>
       <c r="R44" t="n">
-        <v>6779559</v>
+        <v>6779171</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5016,10 +5032,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129934385</v>
+        <v>129934422</v>
       </c>
       <c r="B45" t="n">
-        <v>57738</v>
+        <v>79095</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5027,42 +5043,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>450312</v>
+        <v>450420</v>
       </c>
       <c r="R45" t="n">
-        <v>6779288</v>
+        <v>6779492</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5121,10 +5129,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129934387</v>
+        <v>129934424</v>
       </c>
       <c r="B46" t="n">
-        <v>57738</v>
+        <v>79095</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5132,42 +5140,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>450145</v>
+        <v>450505</v>
       </c>
       <c r="R46" t="n">
-        <v>6779171</v>
+        <v>6779559</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5226,54 +5226,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129934401</v>
+        <v>129934430</v>
       </c>
       <c r="B47" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>450446</v>
+        <v>450405</v>
       </c>
       <c r="R47" t="n">
-        <v>6779375</v>
+        <v>6779582</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5314,7 +5305,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5333,10 +5323,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129934430</v>
+        <v>129934390</v>
       </c>
       <c r="B48" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5344,34 +5334,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>450405</v>
+        <v>450070</v>
       </c>
       <c r="R48" t="n">
-        <v>6779582</v>
+        <v>6779152</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5430,40 +5428,41 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129934390</v>
+        <v>129934401</v>
       </c>
       <c r="B49" t="n">
-        <v>57738</v>
+        <v>8451</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -5473,10 +5472,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>450070</v>
+        <v>450446</v>
       </c>
       <c r="R49" t="n">
-        <v>6779152</v>
+        <v>6779375</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5517,6 +5516,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5535,45 +5535,54 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129934423</v>
+        <v>129934411</v>
       </c>
       <c r="B50" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>450547</v>
+        <v>449925</v>
       </c>
       <c r="R50" t="n">
-        <v>6779569</v>
+        <v>6779047</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5614,6 +5623,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5632,7 +5642,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129934435</v>
+        <v>129934423</v>
       </c>
       <c r="B51" t="n">
         <v>79095</v>
@@ -5667,10 +5677,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>450279</v>
+        <v>450547</v>
       </c>
       <c r="R51" t="n">
-        <v>6779222</v>
+        <v>6779569</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5729,10 +5739,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129934383</v>
+        <v>129934435</v>
       </c>
       <c r="B52" t="n">
-        <v>57738</v>
+        <v>79095</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5740,42 +5750,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>450381</v>
+        <v>450279</v>
       </c>
       <c r="R52" t="n">
-        <v>6779523</v>
+        <v>6779222</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5834,41 +5836,40 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129934411</v>
+        <v>129934383</v>
       </c>
       <c r="B53" t="n">
-        <v>8451</v>
+        <v>57738</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -5878,10 +5879,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>449925</v>
+        <v>450381</v>
       </c>
       <c r="R53" t="n">
-        <v>6779047</v>
+        <v>6779523</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5922,7 +5923,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6038,7 +6038,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129934426</v>
+        <v>129934434</v>
       </c>
       <c r="B55" t="n">
         <v>79095</v>
@@ -6073,10 +6073,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>450499</v>
+        <v>450296</v>
       </c>
       <c r="R55" t="n">
-        <v>6779605</v>
+        <v>6779230</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6135,7 +6135,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129934434</v>
+        <v>129934448</v>
       </c>
       <c r="B56" t="n">
         <v>79095</v>
@@ -6170,10 +6170,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>450296</v>
+        <v>449939</v>
       </c>
       <c r="R56" t="n">
-        <v>6779230</v>
+        <v>6779063</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6232,7 +6232,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129934448</v>
+        <v>129934426</v>
       </c>
       <c r="B57" t="n">
         <v>79095</v>
@@ -6267,10 +6267,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>449939</v>
+        <v>450499</v>
       </c>
       <c r="R57" t="n">
-        <v>6779063</v>
+        <v>6779605</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>

--- a/artfynd/A 54840-2025 artfynd.xlsx
+++ b/artfynd/A 54840-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129934396</v>
+        <v>129934439</v>
       </c>
       <c r="B2" t="n">
-        <v>97704</v>
+        <v>79180</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>450404</v>
+        <v>450124</v>
       </c>
       <c r="R2" t="n">
-        <v>6779584</v>
+        <v>6779174</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -775,7 +775,7 @@
         <v>129934391</v>
       </c>
       <c r="B3" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,32 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129934439</v>
+        <v>129934396</v>
       </c>
       <c r="B4" t="n">
-        <v>79095</v>
+        <v>97791</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>450124</v>
+        <v>450404</v>
       </c>
       <c r="R4" t="n">
-        <v>6779174</v>
+        <v>6779584</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,10 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129934437</v>
+        <v>129934433</v>
       </c>
       <c r="B5" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,10 +1009,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>450194</v>
+        <v>450290</v>
       </c>
       <c r="R5" t="n">
-        <v>6779168</v>
+        <v>6779241</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,10 +1071,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129934433</v>
+        <v>129934437</v>
       </c>
       <c r="B6" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>450290</v>
+        <v>450194</v>
       </c>
       <c r="R6" t="n">
-        <v>6779241</v>
+        <v>6779168</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1171,7 +1171,7 @@
         <v>129934445</v>
       </c>
       <c r="B7" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>129934384</v>
       </c>
       <c r="B8" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>129934377</v>
       </c>
       <c r="B10" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1574,40 +1574,41 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129934392</v>
+        <v>129934410</v>
       </c>
       <c r="B11" t="n">
-        <v>57738</v>
+        <v>8451</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1617,10 +1618,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>449982</v>
+        <v>450367</v>
       </c>
       <c r="R11" t="n">
-        <v>6779088</v>
+        <v>6779462</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1661,6 +1662,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1679,10 +1681,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129934449</v>
+        <v>129934447</v>
       </c>
       <c r="B12" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1714,10 +1716,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>449874</v>
+        <v>449978</v>
       </c>
       <c r="R12" t="n">
-        <v>6779073</v>
+        <v>6779085</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1776,10 +1778,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129934447</v>
+        <v>129934392</v>
       </c>
       <c r="B13" t="n">
-        <v>79095</v>
+        <v>57823</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1787,34 +1789,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>449978</v>
+        <v>449982</v>
       </c>
       <c r="R13" t="n">
-        <v>6779085</v>
+        <v>6779088</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1873,54 +1883,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129934410</v>
+        <v>129934449</v>
       </c>
       <c r="B14" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>450367</v>
+        <v>449874</v>
       </c>
       <c r="R14" t="n">
-        <v>6779462</v>
+        <v>6779073</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1961,7 +1962,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1980,10 +1980,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129934440</v>
+        <v>129934432</v>
       </c>
       <c r="B15" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2015,10 +2015,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>450114</v>
+        <v>450400</v>
       </c>
       <c r="R15" t="n">
-        <v>6779152</v>
+        <v>6779534</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2077,54 +2077,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129934406</v>
+        <v>129934440</v>
       </c>
       <c r="B16" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>450499</v>
+        <v>450114</v>
       </c>
       <c r="R16" t="n">
-        <v>6779570</v>
+        <v>6779152</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2165,7 +2156,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2291,10 +2281,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129934432</v>
+        <v>129934441</v>
       </c>
       <c r="B18" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2326,10 +2316,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>450400</v>
+        <v>450063</v>
       </c>
       <c r="R18" t="n">
-        <v>6779534</v>
+        <v>6779160</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2388,45 +2378,54 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129934441</v>
+        <v>129934406</v>
       </c>
       <c r="B19" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>450063</v>
+        <v>450499</v>
       </c>
       <c r="R19" t="n">
-        <v>6779160</v>
+        <v>6779570</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2467,6 +2466,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2485,45 +2485,54 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129934442</v>
+        <v>129934399</v>
       </c>
       <c r="B20" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>449998</v>
+        <v>450362</v>
       </c>
       <c r="R20" t="n">
-        <v>6779110</v>
+        <v>6779296</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2564,6 +2573,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2585,7 +2595,7 @@
         <v>129934443</v>
       </c>
       <c r="B21" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2679,10 +2689,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129934421</v>
+        <v>129934442</v>
       </c>
       <c r="B22" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2714,10 +2724,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>450436</v>
+        <v>449998</v>
       </c>
       <c r="R22" t="n">
-        <v>6779391</v>
+        <v>6779110</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2776,7 +2786,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129934399</v>
+        <v>129934400</v>
       </c>
       <c r="B23" t="n">
         <v>8451</v>
@@ -2810,7 +2820,7 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2820,10 +2830,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>450362</v>
+        <v>450423</v>
       </c>
       <c r="R23" t="n">
-        <v>6779296</v>
+        <v>6779315</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2883,54 +2893,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129934400</v>
+        <v>129934421</v>
       </c>
       <c r="B24" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>450423</v>
+        <v>450436</v>
       </c>
       <c r="R24" t="n">
-        <v>6779315</v>
+        <v>6779391</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2971,7 +2972,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -2990,41 +2990,40 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129934450</v>
+        <v>129934386</v>
       </c>
       <c r="B25" t="n">
-        <v>5177</v>
+        <v>57823</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3034,10 +3033,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>449945</v>
+        <v>450282</v>
       </c>
       <c r="R25" t="n">
-        <v>6779066</v>
+        <v>6779221</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3078,7 +3077,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3097,40 +3095,41 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129934386</v>
+        <v>129934450</v>
       </c>
       <c r="B26" t="n">
-        <v>57738</v>
+        <v>5177</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3140,10 +3139,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>450282</v>
+        <v>449945</v>
       </c>
       <c r="R26" t="n">
-        <v>6779221</v>
+        <v>6779066</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3184,6 +3183,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3205,7 +3205,7 @@
         <v>129934420</v>
       </c>
       <c r="B27" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         <v>129934427</v>
       </c>
       <c r="B28" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3396,27 +3396,27 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129934413</v>
+        <v>129934395</v>
       </c>
       <c r="B29" t="n">
-        <v>58113</v>
+        <v>57823</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3429,7 +3429,7 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -3439,10 +3439,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>449875</v>
+        <v>449933</v>
       </c>
       <c r="R29" t="n">
-        <v>6779062</v>
+        <v>6779073</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3501,40 +3501,41 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129934395</v>
+        <v>129934408</v>
       </c>
       <c r="B30" t="n">
-        <v>57738</v>
+        <v>8451</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -3544,10 +3545,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>449933</v>
+        <v>450495</v>
       </c>
       <c r="R30" t="n">
-        <v>6779073</v>
+        <v>6779595</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3588,6 +3589,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3606,10 +3608,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129934408</v>
+        <v>129934413</v>
       </c>
       <c r="B31" t="n">
-        <v>8451</v>
+        <v>58198</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3617,30 +3619,29 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>103015</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3650,10 +3651,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>450495</v>
+        <v>449875</v>
       </c>
       <c r="R31" t="n">
-        <v>6779595</v>
+        <v>6779062</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3694,7 +3695,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3713,10 +3713,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129934382</v>
+        <v>129934389</v>
       </c>
       <c r="B32" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3756,10 +3756,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>450440</v>
+        <v>450060</v>
       </c>
       <c r="R32" t="n">
-        <v>6779378</v>
+        <v>6779169</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3818,10 +3818,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129934389</v>
+        <v>129934382</v>
       </c>
       <c r="B33" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3861,10 +3861,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>450060</v>
+        <v>450440</v>
       </c>
       <c r="R33" t="n">
-        <v>6779169</v>
+        <v>6779378</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3923,10 +3923,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129934393</v>
+        <v>129934428</v>
       </c>
       <c r="B34" t="n">
-        <v>57738</v>
+        <v>79180</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3934,42 +3934,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>449973</v>
+        <v>450417</v>
       </c>
       <c r="R34" t="n">
-        <v>6779075</v>
+        <v>6779617</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4028,10 +4020,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129934444</v>
+        <v>129934393</v>
       </c>
       <c r="B35" t="n">
-        <v>79095</v>
+        <v>57823</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4039,34 +4031,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>449991</v>
+        <v>449973</v>
       </c>
       <c r="R35" t="n">
-        <v>6779145</v>
+        <v>6779075</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4125,10 +4125,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129934428</v>
+        <v>129934444</v>
       </c>
       <c r="B36" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4160,10 +4160,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>450417</v>
+        <v>449991</v>
       </c>
       <c r="R36" t="n">
-        <v>6779617</v>
+        <v>6779145</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4332,7 +4332,7 @@
         <v>129934414</v>
       </c>
       <c r="B38" t="n">
-        <v>78852</v>
+        <v>78937</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4426,10 +4426,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129934431</v>
+        <v>129934438</v>
       </c>
       <c r="B39" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4461,10 +4461,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>450414</v>
+        <v>450147</v>
       </c>
       <c r="R39" t="n">
-        <v>6779582</v>
+        <v>6779180</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4523,10 +4523,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129934438</v>
+        <v>129934431</v>
       </c>
       <c r="B40" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4558,10 +4558,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>450147</v>
+        <v>450414</v>
       </c>
       <c r="R40" t="n">
-        <v>6779180</v>
+        <v>6779582</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4623,7 +4623,7 @@
         <v>129934446</v>
       </c>
       <c r="B41" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>129934381</v>
       </c>
       <c r="B42" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4822,10 +4822,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129934385</v>
+        <v>129934387</v>
       </c>
       <c r="B43" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -4865,10 +4865,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>450312</v>
+        <v>450145</v>
       </c>
       <c r="R43" t="n">
-        <v>6779288</v>
+        <v>6779171</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4927,10 +4927,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129934387</v>
+        <v>129934422</v>
       </c>
       <c r="B44" t="n">
-        <v>57738</v>
+        <v>79180</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4938,42 +4938,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>450145</v>
+        <v>450420</v>
       </c>
       <c r="R44" t="n">
-        <v>6779171</v>
+        <v>6779492</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5032,10 +5024,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129934422</v>
+        <v>129934385</v>
       </c>
       <c r="B45" t="n">
-        <v>79095</v>
+        <v>57823</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5043,34 +5035,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>450420</v>
+        <v>450312</v>
       </c>
       <c r="R45" t="n">
-        <v>6779492</v>
+        <v>6779288</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5132,7 +5132,7 @@
         <v>129934424</v>
       </c>
       <c r="B46" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5226,45 +5226,54 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129934430</v>
+        <v>129934401</v>
       </c>
       <c r="B47" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>450405</v>
+        <v>450446</v>
       </c>
       <c r="R47" t="n">
-        <v>6779582</v>
+        <v>6779375</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5305,6 +5314,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5323,10 +5333,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129934390</v>
+        <v>129934430</v>
       </c>
       <c r="B48" t="n">
-        <v>57738</v>
+        <v>79180</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5334,42 +5344,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>450070</v>
+        <v>450405</v>
       </c>
       <c r="R48" t="n">
-        <v>6779152</v>
+        <v>6779582</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5428,41 +5430,40 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129934401</v>
+        <v>129934390</v>
       </c>
       <c r="B49" t="n">
-        <v>8451</v>
+        <v>57823</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -5472,10 +5473,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>450446</v>
+        <v>450070</v>
       </c>
       <c r="R49" t="n">
-        <v>6779375</v>
+        <v>6779152</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5516,7 +5517,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5642,10 +5642,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129934423</v>
+        <v>129934383</v>
       </c>
       <c r="B51" t="n">
-        <v>79095</v>
+        <v>57823</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5653,34 +5653,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>450547</v>
+        <v>450381</v>
       </c>
       <c r="R51" t="n">
-        <v>6779569</v>
+        <v>6779523</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5742,7 +5750,7 @@
         <v>129934435</v>
       </c>
       <c r="B52" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5836,10 +5844,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129934383</v>
+        <v>129934423</v>
       </c>
       <c r="B53" t="n">
-        <v>57738</v>
+        <v>79180</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5847,42 +5855,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>450381</v>
+        <v>450547</v>
       </c>
       <c r="R53" t="n">
-        <v>6779523</v>
+        <v>6779569</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5944,7 +5944,7 @@
         <v>129934429</v>
       </c>
       <c r="B54" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6038,45 +6038,54 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129934434</v>
+        <v>129934409</v>
       </c>
       <c r="B55" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>450296</v>
+        <v>450379</v>
       </c>
       <c r="R55" t="n">
-        <v>6779230</v>
+        <v>6779529</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6117,6 +6126,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6135,10 +6145,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129934448</v>
+        <v>129934426</v>
       </c>
       <c r="B56" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6170,10 +6180,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>449939</v>
+        <v>450499</v>
       </c>
       <c r="R56" t="n">
-        <v>6779063</v>
+        <v>6779605</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6232,10 +6242,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129934426</v>
+        <v>129934434</v>
       </c>
       <c r="B57" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6267,10 +6277,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>450499</v>
+        <v>450296</v>
       </c>
       <c r="R57" t="n">
-        <v>6779605</v>
+        <v>6779230</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6329,54 +6339,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129934409</v>
+        <v>129934448</v>
       </c>
       <c r="B58" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Sälsberg, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>450379</v>
+        <v>449939</v>
       </c>
       <c r="R58" t="n">
-        <v>6779529</v>
+        <v>6779063</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6417,7 +6418,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 54840-2025 artfynd.xlsx
+++ b/artfynd/A 54840-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY62"/>
+  <dimension ref="A1:AZ62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129934420</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129934421</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129934422</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129934423</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129934424</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129934426</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129934427</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129934428</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129934429</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129934430</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129934431</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129934432</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129934433</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129934434</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129934435</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129934436</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129934437</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129934438</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129934439</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129934440</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,6 +2814,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129934441</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2806,6 +2916,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129934442</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2903,6 +3018,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129934443</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3000,6 +3120,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129934444</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3097,6 +3222,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129934445</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3194,6 +3324,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129934446</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3291,6 +3426,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129934447</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3388,6 +3528,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129934448</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3485,6 +3630,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129934449</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3582,6 +3732,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129934414</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3679,6 +3834,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129934377</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3784,6 +3944,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129934381</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3889,6 +4054,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129934382</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3994,6 +4164,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129934383</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4099,6 +4274,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129934384</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4204,6 +4384,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129934385</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4309,6 +4494,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129934386</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4414,6 +4604,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129934387</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4519,6 +4714,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129934389</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4624,6 +4824,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129934390</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4729,6 +4934,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129934391</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4834,6 +5044,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129934392</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4939,6 +5154,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129934393</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5044,6 +5264,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129934395</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5151,6 +5376,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129934450</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5256,6 +5486,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129934413</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5363,6 +5598,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129934399</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5470,6 +5710,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129934400</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5577,6 +5822,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129934401</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5684,6 +5934,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129934402</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5791,6 +6046,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129934403</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5898,6 +6158,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129934404</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6005,6 +6270,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129934405</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6112,6 +6382,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129934406</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6219,6 +6494,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129934407</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6326,6 +6606,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129934408</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6433,6 +6718,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129934409</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6540,6 +6830,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129934410</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6647,6 +6942,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129934411</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6744,6 +7044,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129934396</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6841,8 +7146,76 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129934397</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>